--- a/data.mn/public/datasets/weekly-grocery-prices-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/weekly-grocery-prices-ulaanbaatar.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E288"/>
+  <dimension ref="A1:E296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5904,6 +5904,158 @@
         <v>12285</v>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>618</v>
+      </c>
+      <c r="C289" t="n">
+        <v>3989</v>
+      </c>
+      <c r="D289" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E289" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>618</v>
+      </c>
+      <c r="C290" t="n">
+        <v>3989</v>
+      </c>
+      <c r="D290" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E290" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>618</v>
+      </c>
+      <c r="C291" t="n">
+        <v>3989</v>
+      </c>
+      <c r="D291" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E291" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>618</v>
+      </c>
+      <c r="C292" t="n">
+        <v>3989</v>
+      </c>
+      <c r="D292" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E292" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>620</v>
+      </c>
+      <c r="C293" t="n">
+        <v>4026</v>
+      </c>
+      <c r="D293" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E293" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>621</v>
+      </c>
+      <c r="C294" t="n">
+        <v>4026</v>
+      </c>
+      <c r="D294" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E294" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>621</v>
+      </c>
+      <c r="C295" t="n">
+        <v>4026</v>
+      </c>
+      <c r="D295" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E295" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>621</v>
+      </c>
+      <c r="C296" t="n">
+        <v>4026</v>
+      </c>
+      <c r="D296" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E296" t="n">
+        <v>12285</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5915,14 +6067,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E288"/>
+  <dimension ref="A1:E296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5933,22 +6085,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Өндөг, ш</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Ногоон цай, савласан, 90 г</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Элсэн чихэр, кг</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Ургамлын тос, л</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Элсэн чихэр, кг</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Өндөг, ш</t>
         </is>
       </c>
     </row>
@@ -5959,16 +6111,16 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>374</v>
+      </c>
+      <c r="C2" t="n">
         <v>1572</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4248</v>
       </c>
       <c r="D2" t="n">
         <v>2610</v>
       </c>
       <c r="E2" t="n">
-        <v>374</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="3">
@@ -5978,16 +6130,16 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>374</v>
+      </c>
+      <c r="C3" t="n">
         <v>1572</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4231</v>
       </c>
       <c r="D3" t="n">
         <v>2610</v>
       </c>
       <c r="E3" t="n">
-        <v>374</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="4">
@@ -5997,16 +6149,16 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>378</v>
+      </c>
+      <c r="C4" t="n">
         <v>1572</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4305</v>
       </c>
       <c r="D4" t="n">
         <v>2610</v>
       </c>
       <c r="E4" t="n">
-        <v>378</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="5">
@@ -6016,16 +6168,16 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>378</v>
+      </c>
+      <c r="C5" t="n">
         <v>1572</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4305</v>
       </c>
       <c r="D5" t="n">
         <v>2751</v>
       </c>
       <c r="E5" t="n">
-        <v>378</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="6">
@@ -6035,16 +6187,16 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>400</v>
+      </c>
+      <c r="C6" t="n">
         <v>1572</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4305</v>
       </c>
       <c r="D6" t="n">
         <v>2751</v>
       </c>
       <c r="E6" t="n">
-        <v>400</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="7">
@@ -6054,16 +6206,16 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>400</v>
+      </c>
+      <c r="C7" t="n">
         <v>1572</v>
-      </c>
-      <c r="C7" t="n">
-        <v>4305</v>
       </c>
       <c r="D7" t="n">
         <v>2751</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="8">
@@ -6073,16 +6225,16 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>429</v>
+      </c>
+      <c r="C8" t="n">
         <v>1572</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4305</v>
       </c>
       <c r="D8" t="n">
         <v>2751</v>
       </c>
       <c r="E8" t="n">
-        <v>429</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="9">
@@ -6092,16 +6244,16 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>463</v>
+      </c>
+      <c r="C9" t="n">
         <v>1572</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4305</v>
       </c>
       <c r="D9" t="n">
         <v>2751</v>
       </c>
       <c r="E9" t="n">
-        <v>463</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="10">
@@ -6111,16 +6263,16 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>461</v>
+      </c>
+      <c r="C10" t="n">
         <v>1572</v>
-      </c>
-      <c r="C10" t="n">
-        <v>4305</v>
       </c>
       <c r="D10" t="n">
         <v>2751</v>
       </c>
       <c r="E10" t="n">
-        <v>461</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="11">
@@ -6130,16 +6282,16 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>461</v>
+      </c>
+      <c r="C11" t="n">
         <v>1572</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4305</v>
       </c>
       <c r="D11" t="n">
         <v>2751</v>
       </c>
       <c r="E11" t="n">
-        <v>461</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="12">
@@ -6149,16 +6301,16 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>459</v>
+      </c>
+      <c r="C12" t="n">
         <v>1572</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4305</v>
       </c>
       <c r="D12" t="n">
         <v>2751</v>
       </c>
       <c r="E12" t="n">
-        <v>459</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="13">
@@ -6168,16 +6320,16 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>453</v>
+      </c>
+      <c r="C13" t="n">
         <v>1572</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4288</v>
       </c>
       <c r="D13" t="n">
         <v>2751</v>
       </c>
       <c r="E13" t="n">
-        <v>453</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="14">
@@ -6187,16 +6339,16 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>453</v>
+      </c>
+      <c r="C14" t="n">
         <v>1572</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4288</v>
       </c>
       <c r="D14" t="n">
         <v>2751</v>
       </c>
       <c r="E14" t="n">
-        <v>453</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="15">
@@ -6206,16 +6358,16 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>445</v>
+      </c>
+      <c r="C15" t="n">
         <v>1572</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4288</v>
       </c>
       <c r="D15" t="n">
         <v>2751</v>
       </c>
       <c r="E15" t="n">
-        <v>445</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="16">
@@ -6225,16 +6377,16 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>446</v>
+      </c>
+      <c r="C16" t="n">
         <v>1572</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4288</v>
       </c>
       <c r="D16" t="n">
         <v>2751</v>
       </c>
       <c r="E16" t="n">
-        <v>446</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="17">
@@ -6244,16 +6396,16 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>463</v>
+      </c>
+      <c r="C17" t="n">
         <v>1572</v>
-      </c>
-      <c r="C17" t="n">
-        <v>4288</v>
       </c>
       <c r="D17" t="n">
         <v>2751</v>
       </c>
       <c r="E17" t="n">
-        <v>463</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="18">
@@ -6263,16 +6415,16 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>463</v>
+      </c>
+      <c r="C18" t="n">
         <v>1572</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4288</v>
       </c>
       <c r="D18" t="n">
         <v>2751</v>
       </c>
       <c r="E18" t="n">
-        <v>463</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="19">
@@ -6282,16 +6434,16 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>466</v>
+      </c>
+      <c r="C19" t="n">
         <v>1572</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4288</v>
       </c>
       <c r="D19" t="n">
         <v>2751</v>
       </c>
       <c r="E19" t="n">
-        <v>466</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="20">
@@ -6301,16 +6453,16 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>472</v>
+      </c>
+      <c r="C20" t="n">
         <v>1572</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4288</v>
       </c>
       <c r="D20" t="n">
         <v>2751</v>
       </c>
       <c r="E20" t="n">
-        <v>472</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="21">
@@ -6320,16 +6472,16 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>473</v>
+      </c>
+      <c r="C21" t="n">
         <v>1566</v>
-      </c>
-      <c r="C21" t="n">
-        <v>4288</v>
       </c>
       <c r="D21" t="n">
         <v>2751</v>
       </c>
       <c r="E21" t="n">
-        <v>473</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="22">
@@ -6339,16 +6491,16 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>471</v>
+      </c>
+      <c r="C22" t="n">
         <v>1566</v>
-      </c>
-      <c r="C22" t="n">
-        <v>4288</v>
       </c>
       <c r="D22" t="n">
         <v>2751</v>
       </c>
       <c r="E22" t="n">
-        <v>471</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="23">
@@ -6358,16 +6510,16 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>463</v>
+      </c>
+      <c r="C23" t="n">
         <v>1566</v>
-      </c>
-      <c r="C23" t="n">
-        <v>4288</v>
       </c>
       <c r="D23" t="n">
         <v>2751</v>
       </c>
       <c r="E23" t="n">
-        <v>463</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="24">
@@ -6377,16 +6529,16 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>433</v>
+      </c>
+      <c r="C24" t="n">
         <v>1566</v>
-      </c>
-      <c r="C24" t="n">
-        <v>4395</v>
       </c>
       <c r="D24" t="n">
         <v>2713</v>
       </c>
       <c r="E24" t="n">
-        <v>433</v>
+        <v>4395</v>
       </c>
     </row>
     <row r="25">
@@ -6396,16 +6548,16 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>430</v>
+      </c>
+      <c r="C25" t="n">
         <v>1566</v>
-      </c>
-      <c r="C25" t="n">
-        <v>4395</v>
       </c>
       <c r="D25" t="n">
         <v>2713</v>
       </c>
       <c r="E25" t="n">
-        <v>430</v>
+        <v>4395</v>
       </c>
     </row>
     <row r="26">
@@ -6415,16 +6567,16 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>408</v>
+      </c>
+      <c r="C26" t="n">
         <v>1566</v>
-      </c>
-      <c r="C26" t="n">
-        <v>4420</v>
       </c>
       <c r="D26" t="n">
         <v>2713</v>
       </c>
       <c r="E26" t="n">
-        <v>408</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="27">
@@ -6434,16 +6586,16 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>373</v>
+      </c>
+      <c r="C27" t="n">
         <v>1566</v>
-      </c>
-      <c r="C27" t="n">
-        <v>4451</v>
       </c>
       <c r="D27" t="n">
         <v>2713</v>
       </c>
       <c r="E27" t="n">
-        <v>373</v>
+        <v>4451</v>
       </c>
     </row>
     <row r="28">
@@ -6453,16 +6605,16 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>371</v>
+      </c>
+      <c r="C28" t="n">
         <v>1566</v>
-      </c>
-      <c r="C28" t="n">
-        <v>4469</v>
       </c>
       <c r="D28" t="n">
         <v>2713</v>
       </c>
       <c r="E28" t="n">
-        <v>371</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="29">
@@ -6472,16 +6624,16 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>371</v>
+      </c>
+      <c r="C29" t="n">
         <v>1566</v>
-      </c>
-      <c r="C29" t="n">
-        <v>4469</v>
       </c>
       <c r="D29" t="n">
         <v>2713</v>
       </c>
       <c r="E29" t="n">
-        <v>371</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="30">
@@ -6491,16 +6643,16 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>344</v>
+      </c>
+      <c r="C30" t="n">
         <v>1566</v>
-      </c>
-      <c r="C30" t="n">
-        <v>4710</v>
       </c>
       <c r="D30" t="n">
         <v>2713</v>
       </c>
       <c r="E30" t="n">
-        <v>344</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="31">
@@ -6510,16 +6662,16 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>342</v>
+      </c>
+      <c r="C31" t="n">
         <v>1566</v>
-      </c>
-      <c r="C31" t="n">
-        <v>4710</v>
       </c>
       <c r="D31" t="n">
         <v>2713</v>
       </c>
       <c r="E31" t="n">
-        <v>342</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="32">
@@ -6529,16 +6681,16 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>333</v>
+      </c>
+      <c r="C32" t="n">
         <v>1566</v>
-      </c>
-      <c r="C32" t="n">
-        <v>4774</v>
       </c>
       <c r="D32" t="n">
         <v>2713</v>
       </c>
       <c r="E32" t="n">
-        <v>333</v>
+        <v>4774</v>
       </c>
     </row>
     <row r="33">
@@ -6548,16 +6700,16 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>332</v>
+      </c>
+      <c r="C33" t="n">
         <v>1566</v>
-      </c>
-      <c r="C33" t="n">
-        <v>4774</v>
       </c>
       <c r="D33" t="n">
         <v>2713</v>
       </c>
       <c r="E33" t="n">
-        <v>332</v>
+        <v>4774</v>
       </c>
     </row>
     <row r="34">
@@ -6567,16 +6719,16 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>332</v>
+      </c>
+      <c r="C34" t="n">
         <v>1566</v>
-      </c>
-      <c r="C34" t="n">
-        <v>4821</v>
       </c>
       <c r="D34" t="n">
         <v>2713</v>
       </c>
       <c r="E34" t="n">
-        <v>332</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="35">
@@ -6586,16 +6738,16 @@
         </is>
       </c>
       <c r="B35" t="n">
+        <v>332</v>
+      </c>
+      <c r="C35" t="n">
         <v>1566</v>
-      </c>
-      <c r="C35" t="n">
-        <v>4821</v>
       </c>
       <c r="D35" t="n">
         <v>2800</v>
       </c>
       <c r="E35" t="n">
-        <v>332</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="36">
@@ -6605,16 +6757,16 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>332</v>
+      </c>
+      <c r="C36" t="n">
         <v>1566</v>
-      </c>
-      <c r="C36" t="n">
-        <v>4821</v>
       </c>
       <c r="D36" t="n">
         <v>2800</v>
       </c>
       <c r="E36" t="n">
-        <v>332</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="37">
@@ -6624,16 +6776,16 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>329</v>
+      </c>
+      <c r="C37" t="n">
         <v>1566</v>
-      </c>
-      <c r="C37" t="n">
-        <v>4821</v>
       </c>
       <c r="D37" t="n">
         <v>2800</v>
       </c>
       <c r="E37" t="n">
-        <v>329</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="38">
@@ -6643,16 +6795,16 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>349</v>
+      </c>
+      <c r="C38" t="n">
         <v>1566</v>
-      </c>
-      <c r="C38" t="n">
-        <v>4821</v>
       </c>
       <c r="D38" t="n">
         <v>2800</v>
       </c>
       <c r="E38" t="n">
-        <v>349</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="39">
@@ -6662,16 +6814,16 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>370</v>
+      </c>
+      <c r="C39" t="n">
         <v>1566</v>
-      </c>
-      <c r="C39" t="n">
-        <v>4821</v>
       </c>
       <c r="D39" t="n">
         <v>2800</v>
       </c>
       <c r="E39" t="n">
-        <v>370</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="40">
@@ -6681,16 +6833,16 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>370</v>
+      </c>
+      <c r="C40" t="n">
         <v>1566</v>
-      </c>
-      <c r="C40" t="n">
-        <v>4864</v>
       </c>
       <c r="D40" t="n">
         <v>2800</v>
       </c>
       <c r="E40" t="n">
-        <v>370</v>
+        <v>4864</v>
       </c>
     </row>
     <row r="41">
@@ -6700,16 +6852,16 @@
         </is>
       </c>
       <c r="B41" t="n">
+        <v>409</v>
+      </c>
+      <c r="C41" t="n">
         <v>1566</v>
-      </c>
-      <c r="C41" t="n">
-        <v>4864</v>
       </c>
       <c r="D41" t="n">
         <v>2800</v>
       </c>
       <c r="E41" t="n">
-        <v>409</v>
+        <v>4864</v>
       </c>
     </row>
     <row r="42">
@@ -6719,16 +6871,16 @@
         </is>
       </c>
       <c r="B42" t="n">
+        <v>414</v>
+      </c>
+      <c r="C42" t="n">
         <v>1610</v>
-      </c>
-      <c r="C42" t="n">
-        <v>4864</v>
       </c>
       <c r="D42" t="n">
         <v>2800</v>
       </c>
       <c r="E42" t="n">
-        <v>414</v>
+        <v>4864</v>
       </c>
     </row>
     <row r="43">
@@ -6738,16 +6890,16 @@
         </is>
       </c>
       <c r="B43" t="n">
+        <v>421</v>
+      </c>
+      <c r="C43" t="n">
         <v>1610</v>
-      </c>
-      <c r="C43" t="n">
-        <v>4873</v>
       </c>
       <c r="D43" t="n">
         <v>2800</v>
       </c>
       <c r="E43" t="n">
-        <v>421</v>
+        <v>4873</v>
       </c>
     </row>
     <row r="44">
@@ -6757,16 +6909,16 @@
         </is>
       </c>
       <c r="B44" t="n">
+        <v>421</v>
+      </c>
+      <c r="C44" t="n">
         <v>1902</v>
-      </c>
-      <c r="C44" t="n">
-        <v>5473</v>
       </c>
       <c r="D44" t="n">
         <v>2863</v>
       </c>
       <c r="E44" t="n">
-        <v>421</v>
+        <v>5473</v>
       </c>
     </row>
     <row r="45">
@@ -6776,16 +6928,16 @@
         </is>
       </c>
       <c r="B45" t="n">
+        <v>421</v>
+      </c>
+      <c r="C45" t="n">
         <v>1929</v>
-      </c>
-      <c r="C45" t="n">
-        <v>5473</v>
       </c>
       <c r="D45" t="n">
         <v>2863</v>
       </c>
       <c r="E45" t="n">
-        <v>421</v>
+        <v>5473</v>
       </c>
     </row>
     <row r="46">
@@ -6795,16 +6947,16 @@
         </is>
       </c>
       <c r="B46" t="n">
+        <v>419</v>
+      </c>
+      <c r="C46" t="n">
         <v>1929</v>
-      </c>
-      <c r="C46" t="n">
-        <v>5473</v>
       </c>
       <c r="D46" t="n">
         <v>2863</v>
       </c>
       <c r="E46" t="n">
-        <v>419</v>
+        <v>5473</v>
       </c>
     </row>
     <row r="47">
@@ -6814,16 +6966,16 @@
         </is>
       </c>
       <c r="B47" t="n">
+        <v>425</v>
+      </c>
+      <c r="C47" t="n">
         <v>1929</v>
-      </c>
-      <c r="C47" t="n">
-        <v>5599</v>
       </c>
       <c r="D47" t="n">
         <v>2863</v>
       </c>
       <c r="E47" t="n">
-        <v>425</v>
+        <v>5599</v>
       </c>
     </row>
     <row r="48">
@@ -6833,16 +6985,16 @@
         </is>
       </c>
       <c r="B48" t="n">
+        <v>446</v>
+      </c>
+      <c r="C48" t="n">
         <v>1955</v>
-      </c>
-      <c r="C48" t="n">
-        <v>5637</v>
       </c>
       <c r="D48" t="n">
         <v>2863</v>
       </c>
       <c r="E48" t="n">
-        <v>446</v>
+        <v>5637</v>
       </c>
     </row>
     <row r="49">
@@ -6852,16 +7004,16 @@
         </is>
       </c>
       <c r="B49" t="n">
+        <v>450</v>
+      </c>
+      <c r="C49" t="n">
         <v>1955</v>
-      </c>
-      <c r="C49" t="n">
-        <v>5663</v>
       </c>
       <c r="D49" t="n">
         <v>2863</v>
       </c>
       <c r="E49" t="n">
-        <v>450</v>
+        <v>5663</v>
       </c>
     </row>
     <row r="50">
@@ -6871,16 +7023,16 @@
         </is>
       </c>
       <c r="B50" t="n">
+        <v>465</v>
+      </c>
+      <c r="C50" t="n">
         <v>2012</v>
-      </c>
-      <c r="C50" t="n">
-        <v>5824</v>
       </c>
       <c r="D50" t="n">
         <v>2967</v>
       </c>
       <c r="E50" t="n">
-        <v>465</v>
+        <v>5824</v>
       </c>
     </row>
     <row r="51">
@@ -6890,16 +7042,16 @@
         </is>
       </c>
       <c r="B51" t="n">
+        <v>478</v>
+      </c>
+      <c r="C51" t="n">
         <v>1948</v>
-      </c>
-      <c r="C51" t="n">
-        <v>5770</v>
       </c>
       <c r="D51" t="n">
         <v>3172</v>
       </c>
       <c r="E51" t="n">
-        <v>478</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="52">
@@ -6909,16 +7061,16 @@
         </is>
       </c>
       <c r="B52" t="n">
+        <v>465</v>
+      </c>
+      <c r="C52" t="n">
         <v>1950</v>
-      </c>
-      <c r="C52" t="n">
-        <v>5775</v>
       </c>
       <c r="D52" t="n">
         <v>3108</v>
       </c>
       <c r="E52" t="n">
-        <v>465</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="53">
@@ -6928,16 +7080,16 @@
         </is>
       </c>
       <c r="B53" t="n">
+        <v>470</v>
+      </c>
+      <c r="C53" t="n">
         <v>1964</v>
-      </c>
-      <c r="C53" t="n">
-        <v>5887</v>
       </c>
       <c r="D53" t="n">
         <v>3156</v>
       </c>
       <c r="E53" t="n">
-        <v>470</v>
+        <v>5887</v>
       </c>
     </row>
     <row r="54">
@@ -6947,16 +7099,16 @@
         </is>
       </c>
       <c r="B54" t="n">
+        <v>450</v>
+      </c>
+      <c r="C54" t="n">
         <v>1950</v>
-      </c>
-      <c r="C54" t="n">
-        <v>5929</v>
       </c>
       <c r="D54" t="n">
         <v>3220</v>
       </c>
       <c r="E54" t="n">
-        <v>450</v>
+        <v>5929</v>
       </c>
     </row>
     <row r="55">
@@ -6966,16 +7118,16 @@
         </is>
       </c>
       <c r="B55" t="n">
+        <v>453</v>
+      </c>
+      <c r="C55" t="n">
         <v>1950</v>
-      </c>
-      <c r="C55" t="n">
-        <v>5881</v>
       </c>
       <c r="D55" t="n">
         <v>3220</v>
       </c>
       <c r="E55" t="n">
-        <v>453</v>
+        <v>5881</v>
       </c>
     </row>
     <row r="56">
@@ -6985,16 +7137,16 @@
         </is>
       </c>
       <c r="B56" t="n">
+        <v>450</v>
+      </c>
+      <c r="C56" t="n">
         <v>1950</v>
-      </c>
-      <c r="C56" t="n">
-        <v>5893</v>
       </c>
       <c r="D56" t="n">
         <v>3220</v>
       </c>
       <c r="E56" t="n">
-        <v>450</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="57">
@@ -7004,16 +7156,16 @@
         </is>
       </c>
       <c r="B57" t="n">
+        <v>451</v>
+      </c>
+      <c r="C57" t="n">
         <v>1950</v>
-      </c>
-      <c r="C57" t="n">
-        <v>5893</v>
       </c>
       <c r="D57" t="n">
         <v>3276</v>
       </c>
       <c r="E57" t="n">
-        <v>451</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="58">
@@ -7023,16 +7175,16 @@
         </is>
       </c>
       <c r="B58" t="n">
+        <v>427</v>
+      </c>
+      <c r="C58" t="n">
         <v>1950</v>
-      </c>
-      <c r="C58" t="n">
-        <v>5893</v>
       </c>
       <c r="D58" t="n">
         <v>3276</v>
       </c>
       <c r="E58" t="n">
-        <v>427</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="59">
@@ -7042,16 +7194,16 @@
         </is>
       </c>
       <c r="B59" t="n">
+        <v>408</v>
+      </c>
+      <c r="C59" t="n">
         <v>1950</v>
-      </c>
-      <c r="C59" t="n">
-        <v>5912</v>
       </c>
       <c r="D59" t="n">
         <v>3251</v>
       </c>
       <c r="E59" t="n">
-        <v>408</v>
+        <v>5912</v>
       </c>
     </row>
     <row r="60">
@@ -7061,16 +7213,16 @@
         </is>
       </c>
       <c r="B60" t="n">
+        <v>404</v>
+      </c>
+      <c r="C60" t="n">
         <v>1950</v>
-      </c>
-      <c r="C60" t="n">
-        <v>5851</v>
       </c>
       <c r="D60" t="n">
         <v>3251</v>
       </c>
       <c r="E60" t="n">
-        <v>404</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="61">
@@ -7080,16 +7232,16 @@
         </is>
       </c>
       <c r="B61" t="n">
+        <v>410</v>
+      </c>
+      <c r="C61" t="n">
         <v>1994</v>
-      </c>
-      <c r="C61" t="n">
-        <v>5979</v>
       </c>
       <c r="D61" t="n">
         <v>3251</v>
       </c>
       <c r="E61" t="n">
-        <v>410</v>
+        <v>5979</v>
       </c>
     </row>
     <row r="62">
@@ -7099,16 +7251,16 @@
         </is>
       </c>
       <c r="B62" t="n">
+        <v>413</v>
+      </c>
+      <c r="C62" t="n">
         <v>1994</v>
-      </c>
-      <c r="C62" t="n">
-        <v>5979</v>
       </c>
       <c r="D62" t="n">
         <v>3251</v>
       </c>
       <c r="E62" t="n">
-        <v>413</v>
+        <v>5979</v>
       </c>
     </row>
     <row r="63">
@@ -7118,16 +7270,16 @@
         </is>
       </c>
       <c r="B63" t="n">
+        <v>419</v>
+      </c>
+      <c r="C63" t="n">
         <v>1994</v>
-      </c>
-      <c r="C63" t="n">
-        <v>5932</v>
       </c>
       <c r="D63" t="n">
         <v>3251</v>
       </c>
       <c r="E63" t="n">
-        <v>419</v>
+        <v>5932</v>
       </c>
     </row>
     <row r="64">
@@ -7137,16 +7289,16 @@
         </is>
       </c>
       <c r="B64" t="n">
+        <v>413</v>
+      </c>
+      <c r="C64" t="n">
         <v>1994</v>
-      </c>
-      <c r="C64" t="n">
-        <v>5932</v>
       </c>
       <c r="D64" t="n">
         <v>3251</v>
       </c>
       <c r="E64" t="n">
-        <v>413</v>
+        <v>5932</v>
       </c>
     </row>
     <row r="65">
@@ -7156,16 +7308,16 @@
         </is>
       </c>
       <c r="B65" t="n">
+        <v>413</v>
+      </c>
+      <c r="C65" t="n">
         <v>1994</v>
-      </c>
-      <c r="C65" t="n">
-        <v>5932</v>
       </c>
       <c r="D65" t="n">
         <v>3251</v>
       </c>
       <c r="E65" t="n">
-        <v>413</v>
+        <v>5932</v>
       </c>
     </row>
     <row r="66">
@@ -7175,16 +7327,16 @@
         </is>
       </c>
       <c r="B66" t="n">
+        <v>461</v>
+      </c>
+      <c r="C66" t="n">
         <v>1994</v>
-      </c>
-      <c r="C66" t="n">
-        <v>6631</v>
       </c>
       <c r="D66" t="n">
         <v>3276</v>
       </c>
       <c r="E66" t="n">
-        <v>461</v>
+        <v>6631</v>
       </c>
     </row>
     <row r="67">
@@ -7194,16 +7346,16 @@
         </is>
       </c>
       <c r="B67" t="n">
+        <v>467</v>
+      </c>
+      <c r="C67" t="n">
         <v>1994</v>
-      </c>
-      <c r="C67" t="n">
-        <v>6631</v>
       </c>
       <c r="D67" t="n">
         <v>3276</v>
       </c>
       <c r="E67" t="n">
-        <v>467</v>
+        <v>6631</v>
       </c>
     </row>
     <row r="68">
@@ -7213,16 +7365,16 @@
         </is>
       </c>
       <c r="B68" t="n">
+        <v>470</v>
+      </c>
+      <c r="C68" t="n">
         <v>1994</v>
-      </c>
-      <c r="C68" t="n">
-        <v>6631</v>
       </c>
       <c r="D68" t="n">
         <v>3276</v>
       </c>
       <c r="E68" t="n">
-        <v>470</v>
+        <v>6631</v>
       </c>
     </row>
     <row r="69">
@@ -7232,16 +7384,16 @@
         </is>
       </c>
       <c r="B69" t="n">
+        <v>485</v>
+      </c>
+      <c r="C69" t="n">
         <v>2406</v>
-      </c>
-      <c r="C69" t="n">
-        <v>6631</v>
       </c>
       <c r="D69" t="n">
         <v>3651</v>
       </c>
       <c r="E69" t="n">
-        <v>485</v>
+        <v>6631</v>
       </c>
     </row>
     <row r="70">
@@ -7251,16 +7403,16 @@
         </is>
       </c>
       <c r="B70" t="n">
+        <v>475</v>
+      </c>
+      <c r="C70" t="n">
         <v>2642</v>
-      </c>
-      <c r="C70" t="n">
-        <v>6833</v>
       </c>
       <c r="D70" t="n">
         <v>3651</v>
       </c>
       <c r="E70" t="n">
-        <v>475</v>
+        <v>6833</v>
       </c>
     </row>
     <row r="71">
@@ -7270,16 +7422,16 @@
         </is>
       </c>
       <c r="B71" t="n">
+        <v>473</v>
+      </c>
+      <c r="C71" t="n">
         <v>3134</v>
-      </c>
-      <c r="C71" t="n">
-        <v>6833</v>
       </c>
       <c r="D71" t="n">
         <v>3651</v>
       </c>
       <c r="E71" t="n">
-        <v>473</v>
+        <v>6833</v>
       </c>
     </row>
     <row r="72">
@@ -7289,16 +7441,16 @@
         </is>
       </c>
       <c r="B72" t="n">
+        <v>489</v>
+      </c>
+      <c r="C72" t="n">
         <v>3439</v>
-      </c>
-      <c r="C72" t="n">
-        <v>7254</v>
       </c>
       <c r="D72" t="n">
         <v>3651</v>
       </c>
       <c r="E72" t="n">
-        <v>489</v>
+        <v>7254</v>
       </c>
     </row>
     <row r="73">
@@ -7308,16 +7460,16 @@
         </is>
       </c>
       <c r="B73" t="n">
+        <v>486</v>
+      </c>
+      <c r="C73" t="n">
         <v>3868</v>
-      </c>
-      <c r="C73" t="n">
-        <v>7292</v>
       </c>
       <c r="D73" t="n">
         <v>3651</v>
       </c>
       <c r="E73" t="n">
-        <v>486</v>
+        <v>7292</v>
       </c>
     </row>
     <row r="74">
@@ -7327,16 +7479,16 @@
         </is>
       </c>
       <c r="B74" t="n">
+        <v>473</v>
+      </c>
+      <c r="C74" t="n">
         <v>3796</v>
-      </c>
-      <c r="C74" t="n">
-        <v>7429</v>
       </c>
       <c r="D74" t="n">
         <v>3640</v>
       </c>
       <c r="E74" t="n">
-        <v>473</v>
+        <v>7429</v>
       </c>
     </row>
     <row r="75">
@@ -7346,16 +7498,16 @@
         </is>
       </c>
       <c r="B75" t="n">
+        <v>468</v>
+      </c>
+      <c r="C75" t="n">
         <v>3804</v>
-      </c>
-      <c r="C75" t="n">
-        <v>7733</v>
       </c>
       <c r="D75" t="n">
         <v>3640</v>
       </c>
       <c r="E75" t="n">
-        <v>468</v>
+        <v>7733</v>
       </c>
     </row>
     <row r="76">
@@ -7365,16 +7517,16 @@
         </is>
       </c>
       <c r="B76" t="n">
+        <v>463</v>
+      </c>
+      <c r="C76" t="n">
         <v>3804</v>
-      </c>
-      <c r="C76" t="n">
-        <v>8249</v>
       </c>
       <c r="D76" t="n">
         <v>3748</v>
       </c>
       <c r="E76" t="n">
-        <v>463</v>
+        <v>8249</v>
       </c>
     </row>
     <row r="77">
@@ -7384,16 +7536,16 @@
         </is>
       </c>
       <c r="B77" t="n">
+        <v>470</v>
+      </c>
+      <c r="C77" t="n">
         <v>3772</v>
-      </c>
-      <c r="C77" t="n">
-        <v>8712</v>
       </c>
       <c r="D77" t="n">
         <v>3684</v>
       </c>
       <c r="E77" t="n">
-        <v>470</v>
+        <v>8712</v>
       </c>
     </row>
     <row r="78">
@@ -7403,16 +7555,16 @@
         </is>
       </c>
       <c r="B78" t="n">
+        <v>462</v>
+      </c>
+      <c r="C78" t="n">
         <v>3796</v>
-      </c>
-      <c r="C78" t="n">
-        <v>9516</v>
       </c>
       <c r="D78" t="n">
         <v>3759</v>
       </c>
       <c r="E78" t="n">
-        <v>462</v>
+        <v>9516</v>
       </c>
     </row>
     <row r="79">
@@ -7422,16 +7574,16 @@
         </is>
       </c>
       <c r="B79" t="n">
+        <v>459</v>
+      </c>
+      <c r="C79" t="n">
         <v>3796</v>
-      </c>
-      <c r="C79" t="n">
-        <v>9700</v>
       </c>
       <c r="D79" t="n">
         <v>3759</v>
       </c>
       <c r="E79" t="n">
-        <v>459</v>
+        <v>9700</v>
       </c>
     </row>
     <row r="80">
@@ -7441,16 +7593,16 @@
         </is>
       </c>
       <c r="B80" t="n">
+        <v>463</v>
+      </c>
+      <c r="C80" t="n">
         <v>3796</v>
-      </c>
-      <c r="C80" t="n">
-        <v>9843</v>
       </c>
       <c r="D80" t="n">
         <v>3759</v>
       </c>
       <c r="E80" t="n">
-        <v>463</v>
+        <v>9843</v>
       </c>
     </row>
     <row r="81">
@@ -7460,16 +7612,16 @@
         </is>
       </c>
       <c r="B81" t="n">
+        <v>463</v>
+      </c>
+      <c r="C81" t="n">
         <v>3813</v>
-      </c>
-      <c r="C81" t="n">
-        <v>9870</v>
       </c>
       <c r="D81" t="n">
         <v>3759</v>
       </c>
       <c r="E81" t="n">
-        <v>463</v>
+        <v>9870</v>
       </c>
     </row>
     <row r="82">
@@ -7479,16 +7631,16 @@
         </is>
       </c>
       <c r="B82" t="n">
+        <v>462</v>
+      </c>
+      <c r="C82" t="n">
         <v>3813</v>
-      </c>
-      <c r="C82" t="n">
-        <v>9877</v>
       </c>
       <c r="D82" t="n">
         <v>3759</v>
       </c>
       <c r="E82" t="n">
-        <v>462</v>
+        <v>9877</v>
       </c>
     </row>
     <row r="83">
@@ -7498,16 +7650,16 @@
         </is>
       </c>
       <c r="B83" t="n">
+        <v>463</v>
+      </c>
+      <c r="C83" t="n">
         <v>3813</v>
-      </c>
-      <c r="C83" t="n">
-        <v>10203</v>
       </c>
       <c r="D83" t="n">
         <v>3759</v>
       </c>
       <c r="E83" t="n">
-        <v>463</v>
+        <v>10203</v>
       </c>
     </row>
     <row r="84">
@@ -7517,16 +7669,16 @@
         </is>
       </c>
       <c r="B84" t="n">
+        <v>473</v>
+      </c>
+      <c r="C84" t="n">
         <v>3813</v>
-      </c>
-      <c r="C84" t="n">
-        <v>10203</v>
       </c>
       <c r="D84" t="n">
         <v>3759</v>
       </c>
       <c r="E84" t="n">
-        <v>473</v>
+        <v>10203</v>
       </c>
     </row>
     <row r="85">
@@ -7536,16 +7688,16 @@
         </is>
       </c>
       <c r="B85" t="n">
+        <v>473</v>
+      </c>
+      <c r="C85" t="n">
         <v>3813</v>
-      </c>
-      <c r="C85" t="n">
-        <v>10204</v>
       </c>
       <c r="D85" t="n">
         <v>3759</v>
       </c>
       <c r="E85" t="n">
-        <v>473</v>
+        <v>10204</v>
       </c>
     </row>
     <row r="86">
@@ -7555,16 +7707,16 @@
         </is>
       </c>
       <c r="B86" t="n">
+        <v>472</v>
+      </c>
+      <c r="C86" t="n">
         <v>3813</v>
-      </c>
-      <c r="C86" t="n">
-        <v>10053</v>
       </c>
       <c r="D86" t="n">
         <v>3759</v>
       </c>
       <c r="E86" t="n">
-        <v>472</v>
+        <v>10053</v>
       </c>
     </row>
     <row r="87">
@@ -7574,16 +7726,16 @@
         </is>
       </c>
       <c r="B87" t="n">
+        <v>470</v>
+      </c>
+      <c r="C87" t="n">
         <v>3813</v>
-      </c>
-      <c r="C87" t="n">
-        <v>10192</v>
       </c>
       <c r="D87" t="n">
         <v>3759</v>
       </c>
       <c r="E87" t="n">
-        <v>470</v>
+        <v>10192</v>
       </c>
     </row>
     <row r="88">
@@ -7593,16 +7745,16 @@
         </is>
       </c>
       <c r="B88" t="n">
+        <v>470</v>
+      </c>
+      <c r="C88" t="n">
         <v>3813</v>
-      </c>
-      <c r="C88" t="n">
-        <v>10192</v>
       </c>
       <c r="D88" t="n">
         <v>3759</v>
       </c>
       <c r="E88" t="n">
-        <v>470</v>
+        <v>10192</v>
       </c>
     </row>
     <row r="89">
@@ -7612,16 +7764,16 @@
         </is>
       </c>
       <c r="B89" t="n">
+        <v>470</v>
+      </c>
+      <c r="C89" t="n">
         <v>3813</v>
-      </c>
-      <c r="C89" t="n">
-        <v>8302</v>
       </c>
       <c r="D89" t="n">
         <v>3759</v>
       </c>
       <c r="E89" t="n">
-        <v>470</v>
+        <v>8302</v>
       </c>
     </row>
     <row r="90">
@@ -7631,16 +7783,16 @@
         </is>
       </c>
       <c r="B90" t="n">
+        <v>470</v>
+      </c>
+      <c r="C90" t="n">
         <v>3813</v>
-      </c>
-      <c r="C90" t="n">
-        <v>9542</v>
       </c>
       <c r="D90" t="n">
         <v>3759</v>
       </c>
       <c r="E90" t="n">
-        <v>470</v>
+        <v>9542</v>
       </c>
     </row>
     <row r="91">
@@ -7650,16 +7802,16 @@
         </is>
       </c>
       <c r="B91" t="n">
+        <v>470</v>
+      </c>
+      <c r="C91" t="n">
         <v>3813</v>
-      </c>
-      <c r="C91" t="n">
-        <v>9270</v>
       </c>
       <c r="D91" t="n">
         <v>3759</v>
       </c>
       <c r="E91" t="n">
-        <v>470</v>
+        <v>9270</v>
       </c>
     </row>
     <row r="92">
@@ -7669,16 +7821,16 @@
         </is>
       </c>
       <c r="B92" t="n">
+        <v>478</v>
+      </c>
+      <c r="C92" t="n">
         <v>3804</v>
-      </c>
-      <c r="C92" t="n">
-        <v>9211</v>
       </c>
       <c r="D92" t="n">
         <v>3759</v>
       </c>
       <c r="E92" t="n">
-        <v>478</v>
+        <v>9211</v>
       </c>
     </row>
     <row r="93">
@@ -7688,16 +7840,16 @@
         </is>
       </c>
       <c r="B93" t="n">
+        <v>478</v>
+      </c>
+      <c r="C93" t="n">
         <v>3804</v>
-      </c>
-      <c r="C93" t="n">
-        <v>9175</v>
       </c>
       <c r="D93" t="n">
         <v>3759</v>
       </c>
       <c r="E93" t="n">
-        <v>478</v>
+        <v>9175</v>
       </c>
     </row>
     <row r="94">
@@ -7707,16 +7859,16 @@
         </is>
       </c>
       <c r="B94" t="n">
+        <v>482</v>
+      </c>
+      <c r="C94" t="n">
         <v>3804</v>
-      </c>
-      <c r="C94" t="n">
-        <v>9067</v>
       </c>
       <c r="D94" t="n">
         <v>3759</v>
       </c>
       <c r="E94" t="n">
-        <v>482</v>
+        <v>9067</v>
       </c>
     </row>
     <row r="95">
@@ -7726,16 +7878,16 @@
         </is>
       </c>
       <c r="B95" t="n">
+        <v>496</v>
+      </c>
+      <c r="C95" t="n">
         <v>3804</v>
-      </c>
-      <c r="C95" t="n">
-        <v>9031</v>
       </c>
       <c r="D95" t="n">
         <v>3759</v>
       </c>
       <c r="E95" t="n">
-        <v>496</v>
+        <v>9031</v>
       </c>
     </row>
     <row r="96">
@@ -7745,16 +7897,16 @@
         </is>
       </c>
       <c r="B96" t="n">
+        <v>492</v>
+      </c>
+      <c r="C96" t="n">
         <v>3804</v>
-      </c>
-      <c r="C96" t="n">
-        <v>9031</v>
       </c>
       <c r="D96" t="n">
         <v>3759</v>
       </c>
       <c r="E96" t="n">
-        <v>492</v>
+        <v>9031</v>
       </c>
     </row>
     <row r="97">
@@ -7764,16 +7916,16 @@
         </is>
       </c>
       <c r="B97" t="n">
+        <v>497</v>
+      </c>
+      <c r="C97" t="n">
         <v>3804</v>
-      </c>
-      <c r="C97" t="n">
-        <v>9031</v>
       </c>
       <c r="D97" t="n">
         <v>3759</v>
       </c>
       <c r="E97" t="n">
-        <v>497</v>
+        <v>9031</v>
       </c>
     </row>
     <row r="98">
@@ -7783,16 +7935,16 @@
         </is>
       </c>
       <c r="B98" t="n">
+        <v>508</v>
+      </c>
+      <c r="C98" t="n">
         <v>3804</v>
-      </c>
-      <c r="C98" t="n">
-        <v>8900</v>
       </c>
       <c r="D98" t="n">
         <v>3759</v>
       </c>
       <c r="E98" t="n">
-        <v>508</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="99">
@@ -7802,16 +7954,16 @@
         </is>
       </c>
       <c r="B99" t="n">
+        <v>515</v>
+      </c>
+      <c r="C99" t="n">
         <v>3804</v>
-      </c>
-      <c r="C99" t="n">
-        <v>8270</v>
       </c>
       <c r="D99" t="n">
         <v>3759</v>
       </c>
       <c r="E99" t="n">
-        <v>515</v>
+        <v>8270</v>
       </c>
     </row>
     <row r="100">
@@ -7821,16 +7973,16 @@
         </is>
       </c>
       <c r="B100" t="n">
+        <v>515</v>
+      </c>
+      <c r="C100" t="n">
         <v>3804</v>
-      </c>
-      <c r="C100" t="n">
-        <v>8347</v>
       </c>
       <c r="D100" t="n">
         <v>3771</v>
       </c>
       <c r="E100" t="n">
-        <v>515</v>
+        <v>8347</v>
       </c>
     </row>
     <row r="101">
@@ -7840,16 +7992,16 @@
         </is>
       </c>
       <c r="B101" t="n">
+        <v>537</v>
+      </c>
+      <c r="C101" t="n">
         <v>3804</v>
-      </c>
-      <c r="C101" t="n">
-        <v>8306</v>
       </c>
       <c r="D101" t="n">
         <v>3771</v>
       </c>
       <c r="E101" t="n">
-        <v>537</v>
+        <v>8306</v>
       </c>
     </row>
     <row r="102">
@@ -7859,16 +8011,16 @@
         </is>
       </c>
       <c r="B102" t="n">
+        <v>544</v>
+      </c>
+      <c r="C102" t="n">
         <v>3804</v>
-      </c>
-      <c r="C102" t="n">
-        <v>8231</v>
       </c>
       <c r="D102" t="n">
         <v>3771</v>
       </c>
       <c r="E102" t="n">
-        <v>544</v>
+        <v>8231</v>
       </c>
     </row>
     <row r="103">
@@ -7878,16 +8030,16 @@
         </is>
       </c>
       <c r="B103" t="n">
+        <v>542</v>
+      </c>
+      <c r="C103" t="n">
         <v>3804</v>
-      </c>
-      <c r="C103" t="n">
-        <v>8231</v>
       </c>
       <c r="D103" t="n">
         <v>3771</v>
       </c>
       <c r="E103" t="n">
-        <v>542</v>
+        <v>8231</v>
       </c>
     </row>
     <row r="104">
@@ -7897,16 +8049,16 @@
         </is>
       </c>
       <c r="B104" t="n">
+        <v>543</v>
+      </c>
+      <c r="C104" t="n">
         <v>3804</v>
-      </c>
-      <c r="C104" t="n">
-        <v>8231</v>
       </c>
       <c r="D104" t="n">
         <v>3771</v>
       </c>
       <c r="E104" t="n">
-        <v>543</v>
+        <v>8231</v>
       </c>
     </row>
     <row r="105">
@@ -7916,16 +8068,16 @@
         </is>
       </c>
       <c r="B105" t="n">
+        <v>539</v>
+      </c>
+      <c r="C105" t="n">
         <v>3788</v>
-      </c>
-      <c r="C105" t="n">
-        <v>8250</v>
       </c>
       <c r="D105" t="n">
         <v>3771</v>
       </c>
       <c r="E105" t="n">
-        <v>539</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="106">
@@ -7935,16 +8087,16 @@
         </is>
       </c>
       <c r="B106" t="n">
+        <v>533</v>
+      </c>
+      <c r="C106" t="n">
         <v>3804</v>
-      </c>
-      <c r="C106" t="n">
-        <v>8295</v>
       </c>
       <c r="D106" t="n">
         <v>3771</v>
       </c>
       <c r="E106" t="n">
-        <v>533</v>
+        <v>8295</v>
       </c>
     </row>
     <row r="107">
@@ -7954,16 +8106,16 @@
         </is>
       </c>
       <c r="B107" t="n">
+        <v>523</v>
+      </c>
+      <c r="C107" t="n">
         <v>3804</v>
-      </c>
-      <c r="C107" t="n">
-        <v>8295</v>
       </c>
       <c r="D107" t="n">
         <v>3771</v>
       </c>
       <c r="E107" t="n">
-        <v>523</v>
+        <v>8295</v>
       </c>
     </row>
     <row r="108">
@@ -7973,16 +8125,16 @@
         </is>
       </c>
       <c r="B108" t="n">
+        <v>521</v>
+      </c>
+      <c r="C108" t="n">
         <v>3788</v>
-      </c>
-      <c r="C108" t="n">
-        <v>8413</v>
       </c>
       <c r="D108" t="n">
         <v>3771</v>
       </c>
       <c r="E108" t="n">
-        <v>521</v>
+        <v>8413</v>
       </c>
     </row>
     <row r="109">
@@ -7992,16 +8144,16 @@
         </is>
       </c>
       <c r="B109" t="n">
+        <v>517</v>
+      </c>
+      <c r="C109" t="n">
         <v>3788</v>
-      </c>
-      <c r="C109" t="n">
-        <v>8494</v>
       </c>
       <c r="D109" t="n">
         <v>3771</v>
       </c>
       <c r="E109" t="n">
-        <v>517</v>
+        <v>8494</v>
       </c>
     </row>
     <row r="110">
@@ -8011,16 +8163,16 @@
         </is>
       </c>
       <c r="B110" t="n">
+        <v>516</v>
+      </c>
+      <c r="C110" t="n">
         <v>3788</v>
-      </c>
-      <c r="C110" t="n">
-        <v>8446</v>
       </c>
       <c r="D110" t="n">
         <v>3771</v>
       </c>
       <c r="E110" t="n">
-        <v>516</v>
+        <v>8446</v>
       </c>
     </row>
     <row r="111">
@@ -8030,16 +8182,16 @@
         </is>
       </c>
       <c r="B111" t="n">
+        <v>516</v>
+      </c>
+      <c r="C111" t="n">
         <v>3788</v>
-      </c>
-      <c r="C111" t="n">
-        <v>8448</v>
       </c>
       <c r="D111" t="n">
         <v>3771</v>
       </c>
       <c r="E111" t="n">
-        <v>516</v>
+        <v>8448</v>
       </c>
     </row>
     <row r="112">
@@ -8049,16 +8201,16 @@
         </is>
       </c>
       <c r="B112" t="n">
+        <v>495</v>
+      </c>
+      <c r="C112" t="n">
         <v>3788</v>
-      </c>
-      <c r="C112" t="n">
-        <v>8328</v>
       </c>
       <c r="D112" t="n">
         <v>3771</v>
       </c>
       <c r="E112" t="n">
-        <v>495</v>
+        <v>8328</v>
       </c>
     </row>
     <row r="113">
@@ -8068,16 +8220,16 @@
         </is>
       </c>
       <c r="B113" t="n">
+        <v>520</v>
+      </c>
+      <c r="C113" t="n">
         <v>3788</v>
-      </c>
-      <c r="C113" t="n">
-        <v>8179</v>
       </c>
       <c r="D113" t="n">
         <v>3771</v>
       </c>
       <c r="E113" t="n">
-        <v>520</v>
+        <v>8179</v>
       </c>
     </row>
     <row r="114">
@@ -8087,16 +8239,16 @@
         </is>
       </c>
       <c r="B114" t="n">
+        <v>537</v>
+      </c>
+      <c r="C114" t="n">
         <v>3788</v>
-      </c>
-      <c r="C114" t="n">
-        <v>8179</v>
       </c>
       <c r="D114" t="n">
         <v>3771</v>
       </c>
       <c r="E114" t="n">
-        <v>537</v>
+        <v>8179</v>
       </c>
     </row>
     <row r="115">
@@ -8106,16 +8258,16 @@
         </is>
       </c>
       <c r="B115" t="n">
+        <v>540</v>
+      </c>
+      <c r="C115" t="n">
         <v>3788</v>
-      </c>
-      <c r="C115" t="n">
-        <v>8179</v>
       </c>
       <c r="D115" t="n">
         <v>3771</v>
       </c>
       <c r="E115" t="n">
-        <v>540</v>
+        <v>8179</v>
       </c>
     </row>
     <row r="116">
@@ -8125,16 +8277,16 @@
         </is>
       </c>
       <c r="B116" t="n">
+        <v>546</v>
+      </c>
+      <c r="C116" t="n">
         <v>3788</v>
-      </c>
-      <c r="C116" t="n">
-        <v>8201</v>
       </c>
       <c r="D116" t="n">
         <v>3771</v>
       </c>
       <c r="E116" t="n">
-        <v>546</v>
+        <v>8201</v>
       </c>
     </row>
     <row r="117">
@@ -8144,16 +8296,16 @@
         </is>
       </c>
       <c r="B117" t="n">
+        <v>537</v>
+      </c>
+      <c r="C117" t="n">
         <v>3788</v>
-      </c>
-      <c r="C117" t="n">
-        <v>8201</v>
       </c>
       <c r="D117" t="n">
         <v>3771</v>
       </c>
       <c r="E117" t="n">
-        <v>537</v>
+        <v>8201</v>
       </c>
     </row>
     <row r="118">
@@ -8163,16 +8315,16 @@
         </is>
       </c>
       <c r="B118" t="n">
+        <v>536</v>
+      </c>
+      <c r="C118" t="n">
         <v>3788</v>
-      </c>
-      <c r="C118" t="n">
-        <v>8201</v>
       </c>
       <c r="D118" t="n">
         <v>3771</v>
       </c>
       <c r="E118" t="n">
-        <v>536</v>
+        <v>8201</v>
       </c>
     </row>
     <row r="119">
@@ -8182,16 +8334,16 @@
         </is>
       </c>
       <c r="B119" t="n">
+        <v>539</v>
+      </c>
+      <c r="C119" t="n">
         <v>3788</v>
-      </c>
-      <c r="C119" t="n">
-        <v>8304</v>
       </c>
       <c r="D119" t="n">
         <v>3771</v>
       </c>
       <c r="E119" t="n">
-        <v>539</v>
+        <v>8304</v>
       </c>
     </row>
     <row r="120">
@@ -8201,16 +8353,16 @@
         </is>
       </c>
       <c r="B120" t="n">
+        <v>541</v>
+      </c>
+      <c r="C120" t="n">
         <v>3788</v>
-      </c>
-      <c r="C120" t="n">
-        <v>8298</v>
       </c>
       <c r="D120" t="n">
         <v>3771</v>
       </c>
       <c r="E120" t="n">
-        <v>541</v>
+        <v>8298</v>
       </c>
     </row>
     <row r="121">
@@ -8220,16 +8372,16 @@
         </is>
       </c>
       <c r="B121" t="n">
+        <v>539</v>
+      </c>
+      <c r="C121" t="n">
         <v>3788</v>
-      </c>
-      <c r="C121" t="n">
-        <v>8250</v>
       </c>
       <c r="D121" t="n">
         <v>3771</v>
       </c>
       <c r="E121" t="n">
-        <v>539</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="122">
@@ -8239,16 +8391,16 @@
         </is>
       </c>
       <c r="B122" t="n">
+        <v>535</v>
+      </c>
+      <c r="C122" t="n">
         <v>3788</v>
-      </c>
-      <c r="C122" t="n">
-        <v>8178</v>
       </c>
       <c r="D122" t="n">
         <v>3771</v>
       </c>
       <c r="E122" t="n">
-        <v>535</v>
+        <v>8178</v>
       </c>
     </row>
     <row r="123">
@@ -8258,16 +8410,16 @@
         </is>
       </c>
       <c r="B123" t="n">
+        <v>532</v>
+      </c>
+      <c r="C123" t="n">
         <v>3817</v>
-      </c>
-      <c r="C123" t="n">
-        <v>7960</v>
       </c>
       <c r="D123" t="n">
         <v>3771</v>
       </c>
       <c r="E123" t="n">
-        <v>532</v>
+        <v>7960</v>
       </c>
     </row>
     <row r="124">
@@ -8277,16 +8429,16 @@
         </is>
       </c>
       <c r="B124" t="n">
+        <v>537</v>
+      </c>
+      <c r="C124" t="n">
         <v>3817</v>
-      </c>
-      <c r="C124" t="n">
-        <v>7960</v>
       </c>
       <c r="D124" t="n">
         <v>3771</v>
       </c>
       <c r="E124" t="n">
-        <v>537</v>
+        <v>7960</v>
       </c>
     </row>
     <row r="125">
@@ -8296,16 +8448,16 @@
         </is>
       </c>
       <c r="B125" t="n">
+        <v>524</v>
+      </c>
+      <c r="C125" t="n">
         <v>3817</v>
-      </c>
-      <c r="C125" t="n">
-        <v>7960</v>
       </c>
       <c r="D125" t="n">
         <v>3771</v>
       </c>
       <c r="E125" t="n">
-        <v>524</v>
+        <v>7960</v>
       </c>
     </row>
     <row r="126">
@@ -8315,16 +8467,16 @@
         </is>
       </c>
       <c r="B126" t="n">
+        <v>524</v>
+      </c>
+      <c r="C126" t="n">
         <v>3817</v>
-      </c>
-      <c r="C126" t="n">
-        <v>8011</v>
       </c>
       <c r="D126" t="n">
         <v>3771</v>
       </c>
       <c r="E126" t="n">
-        <v>524</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="127">
@@ -8334,16 +8486,16 @@
         </is>
       </c>
       <c r="B127" t="n">
+        <v>522</v>
+      </c>
+      <c r="C127" t="n">
         <v>3817</v>
-      </c>
-      <c r="C127" t="n">
-        <v>8011</v>
       </c>
       <c r="D127" t="n">
         <v>3771</v>
       </c>
       <c r="E127" t="n">
-        <v>522</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="128">
@@ -8353,16 +8505,16 @@
         </is>
       </c>
       <c r="B128" t="n">
+        <v>525</v>
+      </c>
+      <c r="C128" t="n">
         <v>3618</v>
-      </c>
-      <c r="C128" t="n">
-        <v>8011</v>
       </c>
       <c r="D128" t="n">
         <v>3771</v>
       </c>
       <c r="E128" t="n">
-        <v>525</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="129">
@@ -8372,16 +8524,16 @@
         </is>
       </c>
       <c r="B129" t="n">
+        <v>523</v>
+      </c>
+      <c r="C129" t="n">
         <v>3618</v>
-      </c>
-      <c r="C129" t="n">
-        <v>8011</v>
       </c>
       <c r="D129" t="n">
         <v>3771</v>
       </c>
       <c r="E129" t="n">
-        <v>523</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="130">
@@ -8391,16 +8543,16 @@
         </is>
       </c>
       <c r="B130" t="n">
+        <v>523</v>
+      </c>
+      <c r="C130" t="n">
         <v>3618</v>
-      </c>
-      <c r="C130" t="n">
-        <v>8011</v>
       </c>
       <c r="D130" t="n">
         <v>3771</v>
       </c>
       <c r="E130" t="n">
-        <v>523</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="131">
@@ -8410,16 +8562,16 @@
         </is>
       </c>
       <c r="B131" t="n">
+        <v>510</v>
+      </c>
+      <c r="C131" t="n">
         <v>3618</v>
-      </c>
-      <c r="C131" t="n">
-        <v>8011</v>
       </c>
       <c r="D131" t="n">
         <v>3771</v>
       </c>
       <c r="E131" t="n">
-        <v>510</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="132">
@@ -8429,16 +8581,16 @@
         </is>
       </c>
       <c r="B132" t="n">
+        <v>532</v>
+      </c>
+      <c r="C132" t="n">
         <v>3618</v>
-      </c>
-      <c r="C132" t="n">
-        <v>8011</v>
       </c>
       <c r="D132" t="n">
         <v>3771</v>
       </c>
       <c r="E132" t="n">
-        <v>532</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="133">
@@ -8448,16 +8600,16 @@
         </is>
       </c>
       <c r="B133" t="n">
+        <v>528</v>
+      </c>
+      <c r="C133" t="n">
         <v>3618</v>
-      </c>
-      <c r="C133" t="n">
-        <v>7798</v>
       </c>
       <c r="D133" t="n">
         <v>3771</v>
       </c>
       <c r="E133" t="n">
-        <v>528</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="134">
@@ -8467,16 +8619,16 @@
         </is>
       </c>
       <c r="B134" t="n">
+        <v>524</v>
+      </c>
+      <c r="C134" t="n">
         <v>3618</v>
-      </c>
-      <c r="C134" t="n">
-        <v>7798</v>
       </c>
       <c r="D134" t="n">
         <v>3771</v>
       </c>
       <c r="E134" t="n">
-        <v>524</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="135">
@@ -8486,16 +8638,16 @@
         </is>
       </c>
       <c r="B135" t="n">
+        <v>526</v>
+      </c>
+      <c r="C135" t="n">
         <v>3618</v>
-      </c>
-      <c r="C135" t="n">
-        <v>7798</v>
       </c>
       <c r="D135" t="n">
         <v>3771</v>
       </c>
       <c r="E135" t="n">
-        <v>526</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="136">
@@ -8505,16 +8657,16 @@
         </is>
       </c>
       <c r="B136" t="n">
+        <v>526</v>
+      </c>
+      <c r="C136" t="n">
         <v>3606</v>
-      </c>
-      <c r="C136" t="n">
-        <v>7798</v>
       </c>
       <c r="D136" t="n">
         <v>3771</v>
       </c>
       <c r="E136" t="n">
-        <v>526</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="137">
@@ -8524,16 +8676,16 @@
         </is>
       </c>
       <c r="B137" t="n">
+        <v>523</v>
+      </c>
+      <c r="C137" t="n">
         <v>3606</v>
-      </c>
-      <c r="C137" t="n">
-        <v>7798</v>
       </c>
       <c r="D137" t="n">
         <v>3771</v>
       </c>
       <c r="E137" t="n">
-        <v>523</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="138">
@@ -8543,16 +8695,16 @@
         </is>
       </c>
       <c r="B138" t="n">
+        <v>524</v>
+      </c>
+      <c r="C138" t="n">
         <v>3625</v>
-      </c>
-      <c r="C138" t="n">
-        <v>7798</v>
       </c>
       <c r="D138" t="n">
         <v>4035</v>
       </c>
       <c r="E138" t="n">
-        <v>524</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="139">
@@ -8562,16 +8714,16 @@
         </is>
       </c>
       <c r="B139" t="n">
+        <v>524</v>
+      </c>
+      <c r="C139" t="n">
         <v>3621</v>
-      </c>
-      <c r="C139" t="n">
-        <v>7798</v>
       </c>
       <c r="D139" t="n">
         <v>3997</v>
       </c>
       <c r="E139" t="n">
-        <v>524</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="140">
@@ -8581,16 +8733,16 @@
         </is>
       </c>
       <c r="B140" t="n">
+        <v>524</v>
+      </c>
+      <c r="C140" t="n">
         <v>3621</v>
-      </c>
-      <c r="C140" t="n">
-        <v>7798</v>
       </c>
       <c r="D140" t="n">
         <v>5023</v>
       </c>
       <c r="E140" t="n">
-        <v>524</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="141">
@@ -8600,16 +8752,16 @@
         </is>
       </c>
       <c r="B141" t="n">
+        <v>527</v>
+      </c>
+      <c r="C141" t="n">
         <v>3621</v>
-      </c>
-      <c r="C141" t="n">
-        <v>7798</v>
       </c>
       <c r="D141" t="n">
         <v>5023</v>
       </c>
       <c r="E141" t="n">
-        <v>527</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="142">
@@ -8619,16 +8771,16 @@
         </is>
       </c>
       <c r="B142" t="n">
+        <v>561</v>
+      </c>
+      <c r="C142" t="n">
         <v>3798</v>
-      </c>
-      <c r="C142" t="n">
-        <v>7798</v>
       </c>
       <c r="D142" t="n">
         <v>5023</v>
       </c>
       <c r="E142" t="n">
-        <v>561</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="143">
@@ -8638,16 +8790,16 @@
         </is>
       </c>
       <c r="B143" t="n">
+        <v>567</v>
+      </c>
+      <c r="C143" t="n">
         <v>3798</v>
-      </c>
-      <c r="C143" t="n">
-        <v>7798</v>
       </c>
       <c r="D143" t="n">
         <v>5023</v>
       </c>
       <c r="E143" t="n">
-        <v>567</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="144">
@@ -8657,16 +8809,16 @@
         </is>
       </c>
       <c r="B144" t="n">
+        <v>585</v>
+      </c>
+      <c r="C144" t="n">
         <v>3798</v>
-      </c>
-      <c r="C144" t="n">
-        <v>7378</v>
       </c>
       <c r="D144" t="n">
         <v>5042</v>
       </c>
       <c r="E144" t="n">
-        <v>585</v>
+        <v>7378</v>
       </c>
     </row>
     <row r="145">
@@ -8676,16 +8828,16 @@
         </is>
       </c>
       <c r="B145" t="n">
+        <v>588</v>
+      </c>
+      <c r="C145" t="n">
         <v>3798</v>
-      </c>
-      <c r="C145" t="n">
-        <v>7163</v>
       </c>
       <c r="D145" t="n">
         <v>5042</v>
       </c>
       <c r="E145" t="n">
-        <v>588</v>
+        <v>7163</v>
       </c>
     </row>
     <row r="146">
@@ -8695,16 +8847,16 @@
         </is>
       </c>
       <c r="B146" t="n">
+        <v>595</v>
+      </c>
+      <c r="C146" t="n">
         <v>3812</v>
-      </c>
-      <c r="C146" t="n">
-        <v>7160</v>
       </c>
       <c r="D146" t="n">
         <v>5042</v>
       </c>
       <c r="E146" t="n">
-        <v>595</v>
+        <v>7160</v>
       </c>
     </row>
     <row r="147">
@@ -8714,16 +8866,16 @@
         </is>
       </c>
       <c r="B147" t="n">
+        <v>600</v>
+      </c>
+      <c r="C147" t="n">
         <v>3812</v>
-      </c>
-      <c r="C147" t="n">
-        <v>7160</v>
       </c>
       <c r="D147" t="n">
         <v>5042</v>
       </c>
       <c r="E147" t="n">
-        <v>600</v>
+        <v>7160</v>
       </c>
     </row>
     <row r="148">
@@ -8733,16 +8885,16 @@
         </is>
       </c>
       <c r="B148" t="n">
+        <v>610</v>
+      </c>
+      <c r="C148" t="n">
         <v>3830</v>
-      </c>
-      <c r="C148" t="n">
-        <v>6747</v>
       </c>
       <c r="D148" t="n">
         <v>5042</v>
       </c>
       <c r="E148" t="n">
-        <v>610</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="149">
@@ -8752,16 +8904,16 @@
         </is>
       </c>
       <c r="B149" t="n">
+        <v>603</v>
+      </c>
+      <c r="C149" t="n">
         <v>3830</v>
-      </c>
-      <c r="C149" t="n">
-        <v>6747</v>
       </c>
       <c r="D149" t="n">
         <v>5042</v>
       </c>
       <c r="E149" t="n">
-        <v>603</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="150">
@@ -8771,16 +8923,16 @@
         </is>
       </c>
       <c r="B150" t="n">
+        <v>603</v>
+      </c>
+      <c r="C150" t="n">
         <v>3830</v>
-      </c>
-      <c r="C150" t="n">
-        <v>6747</v>
       </c>
       <c r="D150" t="n">
         <v>5042</v>
       </c>
       <c r="E150" t="n">
-        <v>603</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="151">
@@ -8790,16 +8942,16 @@
         </is>
       </c>
       <c r="B151" t="n">
+        <v>603</v>
+      </c>
+      <c r="C151" t="n">
         <v>3830</v>
-      </c>
-      <c r="C151" t="n">
-        <v>6747</v>
       </c>
       <c r="D151" t="n">
         <v>5042</v>
       </c>
       <c r="E151" t="n">
-        <v>603</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="152">
@@ -8809,16 +8961,16 @@
         </is>
       </c>
       <c r="B152" t="n">
+        <v>604</v>
+      </c>
+      <c r="C152" t="n">
         <v>3830</v>
-      </c>
-      <c r="C152" t="n">
-        <v>6747</v>
       </c>
       <c r="D152" t="n">
         <v>5042</v>
       </c>
       <c r="E152" t="n">
-        <v>604</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="153">
@@ -8828,16 +8980,16 @@
         </is>
       </c>
       <c r="B153" t="n">
+        <v>598</v>
+      </c>
+      <c r="C153" t="n">
         <v>3830</v>
-      </c>
-      <c r="C153" t="n">
-        <v>6747</v>
       </c>
       <c r="D153" t="n">
         <v>5042</v>
       </c>
       <c r="E153" t="n">
-        <v>598</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="154">
@@ -8847,16 +8999,16 @@
         </is>
       </c>
       <c r="B154" t="n">
+        <v>600</v>
+      </c>
+      <c r="C154" t="n">
         <v>3830</v>
-      </c>
-      <c r="C154" t="n">
-        <v>6747</v>
       </c>
       <c r="D154" t="n">
         <v>5042</v>
       </c>
       <c r="E154" t="n">
-        <v>600</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="155">
@@ -8866,16 +9018,16 @@
         </is>
       </c>
       <c r="B155" t="n">
+        <v>602</v>
+      </c>
+      <c r="C155" t="n">
         <v>3830</v>
-      </c>
-      <c r="C155" t="n">
-        <v>6747</v>
       </c>
       <c r="D155" t="n">
         <v>5042</v>
       </c>
       <c r="E155" t="n">
-        <v>602</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="156">
@@ -8885,16 +9037,16 @@
         </is>
       </c>
       <c r="B156" t="n">
+        <v>600</v>
+      </c>
+      <c r="C156" t="n">
         <v>3830</v>
-      </c>
-      <c r="C156" t="n">
-        <v>6747</v>
       </c>
       <c r="D156" t="n">
         <v>5042</v>
       </c>
       <c r="E156" t="n">
-        <v>600</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="157">
@@ -8904,16 +9056,16 @@
         </is>
       </c>
       <c r="B157" t="n">
+        <v>600</v>
+      </c>
+      <c r="C157" t="n">
         <v>3830</v>
-      </c>
-      <c r="C157" t="n">
-        <v>6747</v>
       </c>
       <c r="D157" t="n">
         <v>5042</v>
       </c>
       <c r="E157" t="n">
-        <v>600</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="158">
@@ -8923,16 +9075,16 @@
         </is>
       </c>
       <c r="B158" t="n">
+        <v>600</v>
+      </c>
+      <c r="C158" t="n">
         <v>3830</v>
-      </c>
-      <c r="C158" t="n">
-        <v>6747</v>
       </c>
       <c r="D158" t="n">
         <v>5042</v>
       </c>
       <c r="E158" t="n">
-        <v>600</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="159">
@@ -8942,16 +9094,16 @@
         </is>
       </c>
       <c r="B159" t="n">
+        <v>593</v>
+      </c>
+      <c r="C159" t="n">
         <v>3830</v>
-      </c>
-      <c r="C159" t="n">
-        <v>6747</v>
       </c>
       <c r="D159" t="n">
         <v>5042</v>
       </c>
       <c r="E159" t="n">
-        <v>593</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="160">
@@ -8961,16 +9113,16 @@
         </is>
       </c>
       <c r="B160" t="n">
+        <v>598</v>
+      </c>
+      <c r="C160" t="n">
         <v>3830</v>
-      </c>
-      <c r="C160" t="n">
-        <v>6747</v>
       </c>
       <c r="D160" t="n">
         <v>5042</v>
       </c>
       <c r="E160" t="n">
-        <v>598</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="161">
@@ -8980,16 +9132,16 @@
         </is>
       </c>
       <c r="B161" t="n">
+        <v>599</v>
+      </c>
+      <c r="C161" t="n">
         <v>3830</v>
-      </c>
-      <c r="C161" t="n">
-        <v>6747</v>
       </c>
       <c r="D161" t="n">
         <v>5042</v>
       </c>
       <c r="E161" t="n">
-        <v>599</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="162">
@@ -8999,16 +9151,16 @@
         </is>
       </c>
       <c r="B162" t="n">
+        <v>596</v>
+      </c>
+      <c r="C162" t="n">
         <v>3830</v>
-      </c>
-      <c r="C162" t="n">
-        <v>6747</v>
       </c>
       <c r="D162" t="n">
         <v>5042</v>
       </c>
       <c r="E162" t="n">
-        <v>596</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="163">
@@ -9018,16 +9170,16 @@
         </is>
       </c>
       <c r="B163" t="n">
+        <v>597</v>
+      </c>
+      <c r="C163" t="n">
         <v>3830</v>
-      </c>
-      <c r="C163" t="n">
-        <v>6747</v>
       </c>
       <c r="D163" t="n">
         <v>5042</v>
       </c>
       <c r="E163" t="n">
-        <v>597</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="164">
@@ -9037,16 +9189,16 @@
         </is>
       </c>
       <c r="B164" t="n">
+        <v>605</v>
+      </c>
+      <c r="C164" t="n">
         <v>3830</v>
-      </c>
-      <c r="C164" t="n">
-        <v>6747</v>
       </c>
       <c r="D164" t="n">
         <v>5042</v>
       </c>
       <c r="E164" t="n">
-        <v>605</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="165">
@@ -9056,16 +9208,16 @@
         </is>
       </c>
       <c r="B165" t="n">
+        <v>635</v>
+      </c>
+      <c r="C165" t="n">
         <v>3806</v>
-      </c>
-      <c r="C165" t="n">
-        <v>6747</v>
       </c>
       <c r="D165" t="n">
         <v>5042</v>
       </c>
       <c r="E165" t="n">
-        <v>635</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="166">
@@ -9075,16 +9227,16 @@
         </is>
       </c>
       <c r="B166" t="n">
+        <v>643</v>
+      </c>
+      <c r="C166" t="n">
         <v>3806</v>
-      </c>
-      <c r="C166" t="n">
-        <v>6821</v>
       </c>
       <c r="D166" t="n">
         <v>5042</v>
       </c>
       <c r="E166" t="n">
-        <v>643</v>
+        <v>6821</v>
       </c>
     </row>
     <row r="167">
@@ -9094,16 +9246,16 @@
         </is>
       </c>
       <c r="B167" t="n">
+        <v>643</v>
+      </c>
+      <c r="C167" t="n">
         <v>3806</v>
-      </c>
-      <c r="C167" t="n">
-        <v>6747</v>
       </c>
       <c r="D167" t="n">
         <v>5042</v>
       </c>
       <c r="E167" t="n">
-        <v>643</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="168">
@@ -9113,16 +9265,16 @@
         </is>
       </c>
       <c r="B168" t="n">
+        <v>648</v>
+      </c>
+      <c r="C168" t="n">
         <v>3806</v>
-      </c>
-      <c r="C168" t="n">
-        <v>6792</v>
       </c>
       <c r="D168" t="n">
         <v>5042</v>
       </c>
       <c r="E168" t="n">
-        <v>648</v>
+        <v>6792</v>
       </c>
     </row>
     <row r="169">
@@ -9132,16 +9284,16 @@
         </is>
       </c>
       <c r="B169" t="n">
+        <v>650</v>
+      </c>
+      <c r="C169" t="n">
         <v>3806</v>
-      </c>
-      <c r="C169" t="n">
-        <v>6712</v>
       </c>
       <c r="D169" t="n">
         <v>5042</v>
       </c>
       <c r="E169" t="n">
-        <v>650</v>
+        <v>6712</v>
       </c>
     </row>
     <row r="170">
@@ -9151,16 +9303,16 @@
         </is>
       </c>
       <c r="B170" t="n">
+        <v>650</v>
+      </c>
+      <c r="C170" t="n">
         <v>3816</v>
-      </c>
-      <c r="C170" t="n">
-        <v>6755</v>
       </c>
       <c r="D170" t="n">
         <v>5042</v>
       </c>
       <c r="E170" t="n">
-        <v>650</v>
+        <v>6755</v>
       </c>
     </row>
     <row r="171">
@@ -9170,16 +9322,16 @@
         </is>
       </c>
       <c r="B171" t="n">
+        <v>644</v>
+      </c>
+      <c r="C171" t="n">
         <v>3816</v>
-      </c>
-      <c r="C171" t="n">
-        <v>6640</v>
       </c>
       <c r="D171" t="n">
         <v>5042</v>
       </c>
       <c r="E171" t="n">
-        <v>644</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="172">
@@ -9189,16 +9341,16 @@
         </is>
       </c>
       <c r="B172" t="n">
+        <v>645</v>
+      </c>
+      <c r="C172" t="n">
         <v>3764</v>
-      </c>
-      <c r="C172" t="n">
-        <v>6564</v>
       </c>
       <c r="D172" t="n">
         <v>5042</v>
       </c>
       <c r="E172" t="n">
-        <v>645</v>
+        <v>6564</v>
       </c>
     </row>
     <row r="173">
@@ -9208,16 +9360,16 @@
         </is>
       </c>
       <c r="B173" t="n">
+        <v>650</v>
+      </c>
+      <c r="C173" t="n">
         <v>3780</v>
-      </c>
-      <c r="C173" t="n">
-        <v>6556</v>
       </c>
       <c r="D173" t="n">
         <v>5042</v>
       </c>
       <c r="E173" t="n">
-        <v>650</v>
+        <v>6556</v>
       </c>
     </row>
     <row r="174">
@@ -9227,16 +9379,16 @@
         </is>
       </c>
       <c r="B174" t="n">
+        <v>645</v>
+      </c>
+      <c r="C174" t="n">
         <v>3799</v>
-      </c>
-      <c r="C174" t="n">
-        <v>6658</v>
       </c>
       <c r="D174" t="n">
         <v>5042</v>
       </c>
       <c r="E174" t="n">
-        <v>645</v>
+        <v>6658</v>
       </c>
     </row>
     <row r="175">
@@ -9246,16 +9398,16 @@
         </is>
       </c>
       <c r="B175" t="n">
+        <v>646</v>
+      </c>
+      <c r="C175" t="n">
         <v>3872</v>
-      </c>
-      <c r="C175" t="n">
-        <v>6658</v>
       </c>
       <c r="D175" t="n">
         <v>5042</v>
       </c>
       <c r="E175" t="n">
-        <v>646</v>
+        <v>6658</v>
       </c>
     </row>
     <row r="176">
@@ -9265,16 +9417,16 @@
         </is>
       </c>
       <c r="B176" t="n">
+        <v>645</v>
+      </c>
+      <c r="C176" t="n">
         <v>3872</v>
-      </c>
-      <c r="C176" t="n">
-        <v>6569</v>
       </c>
       <c r="D176" t="n">
         <v>5042</v>
       </c>
       <c r="E176" t="n">
-        <v>645</v>
+        <v>6569</v>
       </c>
     </row>
     <row r="177">
@@ -9284,16 +9436,16 @@
         </is>
       </c>
       <c r="B177" t="n">
+        <v>653</v>
+      </c>
+      <c r="C177" t="n">
         <v>3880</v>
-      </c>
-      <c r="C177" t="n">
-        <v>6569</v>
       </c>
       <c r="D177" t="n">
         <v>5042</v>
       </c>
       <c r="E177" t="n">
-        <v>653</v>
+        <v>6569</v>
       </c>
     </row>
     <row r="178">
@@ -9303,16 +9455,16 @@
         </is>
       </c>
       <c r="B178" t="n">
+        <v>649</v>
+      </c>
+      <c r="C178" t="n">
         <v>3905</v>
-      </c>
-      <c r="C178" t="n">
-        <v>6569</v>
       </c>
       <c r="D178" t="n">
         <v>5042</v>
       </c>
       <c r="E178" t="n">
-        <v>649</v>
+        <v>6569</v>
       </c>
     </row>
     <row r="179">
@@ -9322,16 +9474,16 @@
         </is>
       </c>
       <c r="B179" t="n">
+        <v>649</v>
+      </c>
+      <c r="C179" t="n">
         <v>3905</v>
-      </c>
-      <c r="C179" t="n">
-        <v>6569</v>
       </c>
       <c r="D179" t="n">
         <v>5042</v>
       </c>
       <c r="E179" t="n">
-        <v>649</v>
+        <v>6569</v>
       </c>
     </row>
     <row r="180">
@@ -9341,16 +9493,16 @@
         </is>
       </c>
       <c r="B180" t="n">
+        <v>639</v>
+      </c>
+      <c r="C180" t="n">
         <v>3905</v>
-      </c>
-      <c r="C180" t="n">
-        <v>6482</v>
       </c>
       <c r="D180" t="n">
         <v>5042</v>
       </c>
       <c r="E180" t="n">
-        <v>639</v>
+        <v>6482</v>
       </c>
     </row>
     <row r="181">
@@ -9360,16 +9512,16 @@
         </is>
       </c>
       <c r="B181" t="n">
+        <v>639</v>
+      </c>
+      <c r="C181" t="n">
         <v>3905</v>
-      </c>
-      <c r="C181" t="n">
-        <v>6526</v>
       </c>
       <c r="D181" t="n">
         <v>5042</v>
       </c>
       <c r="E181" t="n">
-        <v>639</v>
+        <v>6526</v>
       </c>
     </row>
     <row r="182">
@@ -9379,16 +9531,16 @@
         </is>
       </c>
       <c r="B182" t="n">
+        <v>638</v>
+      </c>
+      <c r="C182" t="n">
         <v>3905</v>
-      </c>
-      <c r="C182" t="n">
-        <v>6478</v>
       </c>
       <c r="D182" t="n">
         <v>5042</v>
       </c>
       <c r="E182" t="n">
-        <v>638</v>
+        <v>6478</v>
       </c>
     </row>
     <row r="183">
@@ -9398,16 +9550,16 @@
         </is>
       </c>
       <c r="B183" t="n">
+        <v>635</v>
+      </c>
+      <c r="C183" t="n">
         <v>3905</v>
-      </c>
-      <c r="C183" t="n">
-        <v>6478</v>
       </c>
       <c r="D183" t="n">
         <v>5042</v>
       </c>
       <c r="E183" t="n">
-        <v>635</v>
+        <v>6478</v>
       </c>
     </row>
     <row r="184">
@@ -9417,16 +9569,16 @@
         </is>
       </c>
       <c r="B184" t="n">
+        <v>622</v>
+      </c>
+      <c r="C184" t="n">
         <v>3905</v>
-      </c>
-      <c r="C184" t="n">
-        <v>6478</v>
       </c>
       <c r="D184" t="n">
         <v>5042</v>
       </c>
       <c r="E184" t="n">
-        <v>622</v>
+        <v>6478</v>
       </c>
     </row>
     <row r="185">
@@ -9436,16 +9588,16 @@
         </is>
       </c>
       <c r="B185" t="n">
+        <v>622</v>
+      </c>
+      <c r="C185" t="n">
         <v>3905</v>
-      </c>
-      <c r="C185" t="n">
-        <v>6478</v>
       </c>
       <c r="D185" t="n">
         <v>5042</v>
       </c>
       <c r="E185" t="n">
-        <v>622</v>
+        <v>6478</v>
       </c>
     </row>
     <row r="186">
@@ -9455,16 +9607,16 @@
         </is>
       </c>
       <c r="B186" t="n">
+        <v>622</v>
+      </c>
+      <c r="C186" t="n">
         <v>3903</v>
-      </c>
-      <c r="C186" t="n">
-        <v>6495</v>
       </c>
       <c r="D186" t="n">
         <v>5042</v>
       </c>
       <c r="E186" t="n">
-        <v>622</v>
+        <v>6495</v>
       </c>
     </row>
     <row r="187">
@@ -9474,16 +9626,16 @@
         </is>
       </c>
       <c r="B187" t="n">
+        <v>623</v>
+      </c>
+      <c r="C187" t="n">
         <v>3903</v>
-      </c>
-      <c r="C187" t="n">
-        <v>6495</v>
       </c>
       <c r="D187" t="n">
         <v>5042</v>
       </c>
       <c r="E187" t="n">
-        <v>623</v>
+        <v>6495</v>
       </c>
     </row>
     <row r="188">
@@ -9493,16 +9645,16 @@
         </is>
       </c>
       <c r="B188" t="n">
+        <v>624</v>
+      </c>
+      <c r="C188" t="n">
         <v>3903</v>
-      </c>
-      <c r="C188" t="n">
-        <v>6495</v>
       </c>
       <c r="D188" t="n">
         <v>5042</v>
       </c>
       <c r="E188" t="n">
-        <v>624</v>
+        <v>6495</v>
       </c>
     </row>
     <row r="189">
@@ -9512,16 +9664,16 @@
         </is>
       </c>
       <c r="B189" t="n">
+        <v>624</v>
+      </c>
+      <c r="C189" t="n">
         <v>3903</v>
-      </c>
-      <c r="C189" t="n">
-        <v>6451</v>
       </c>
       <c r="D189" t="n">
         <v>5042</v>
       </c>
       <c r="E189" t="n">
-        <v>624</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="190">
@@ -9531,16 +9683,16 @@
         </is>
       </c>
       <c r="B190" t="n">
+        <v>626</v>
+      </c>
+      <c r="C190" t="n">
         <v>3903</v>
-      </c>
-      <c r="C190" t="n">
-        <v>6451</v>
       </c>
       <c r="D190" t="n">
         <v>5042</v>
       </c>
       <c r="E190" t="n">
-        <v>626</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="191">
@@ -9550,16 +9702,16 @@
         </is>
       </c>
       <c r="B191" t="n">
+        <v>626</v>
+      </c>
+      <c r="C191" t="n">
         <v>3888</v>
-      </c>
-      <c r="C191" t="n">
-        <v>6451</v>
       </c>
       <c r="D191" t="n">
         <v>4986</v>
       </c>
       <c r="E191" t="n">
-        <v>626</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="192">
@@ -9569,16 +9721,16 @@
         </is>
       </c>
       <c r="B192" t="n">
+        <v>626</v>
+      </c>
+      <c r="C192" t="n">
         <v>3888</v>
-      </c>
-      <c r="C192" t="n">
-        <v>6451</v>
       </c>
       <c r="D192" t="n">
         <v>4986</v>
       </c>
       <c r="E192" t="n">
-        <v>626</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="193">
@@ -9588,16 +9740,16 @@
         </is>
       </c>
       <c r="B193" t="n">
+        <v>626</v>
+      </c>
+      <c r="C193" t="n">
         <v>3888</v>
-      </c>
-      <c r="C193" t="n">
-        <v>6601</v>
       </c>
       <c r="D193" t="n">
         <v>4986</v>
       </c>
       <c r="E193" t="n">
-        <v>626</v>
+        <v>6601</v>
       </c>
     </row>
     <row r="194">
@@ -9607,16 +9759,16 @@
         </is>
       </c>
       <c r="B194" t="n">
+        <v>626</v>
+      </c>
+      <c r="C194" t="n">
         <v>3888</v>
-      </c>
-      <c r="C194" t="n">
-        <v>6145</v>
       </c>
       <c r="D194" t="n">
         <v>4986</v>
       </c>
       <c r="E194" t="n">
-        <v>626</v>
+        <v>6145</v>
       </c>
     </row>
     <row r="195">
@@ -9626,16 +9778,16 @@
         </is>
       </c>
       <c r="B195" t="n">
+        <v>622</v>
+      </c>
+      <c r="C195" t="n">
         <v>3896</v>
-      </c>
-      <c r="C195" t="n">
-        <v>5986</v>
       </c>
       <c r="D195" t="n">
         <v>4986</v>
       </c>
       <c r="E195" t="n">
-        <v>622</v>
+        <v>5986</v>
       </c>
     </row>
     <row r="196">
@@ -9645,16 +9797,16 @@
         </is>
       </c>
       <c r="B196" t="n">
+        <v>622</v>
+      </c>
+      <c r="C196" t="n">
         <v>3896</v>
-      </c>
-      <c r="C196" t="n">
-        <v>6145</v>
       </c>
       <c r="D196" t="n">
         <v>4986</v>
       </c>
       <c r="E196" t="n">
-        <v>622</v>
+        <v>6145</v>
       </c>
     </row>
     <row r="197">
@@ -9664,16 +9816,16 @@
         </is>
       </c>
       <c r="B197" t="n">
+        <v>621</v>
+      </c>
+      <c r="C197" t="n">
         <v>3896</v>
-      </c>
-      <c r="C197" t="n">
-        <v>6332</v>
       </c>
       <c r="D197" t="n">
         <v>4986</v>
       </c>
       <c r="E197" t="n">
-        <v>621</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="198">
@@ -9683,16 +9835,16 @@
         </is>
       </c>
       <c r="B198" t="n">
+        <v>621</v>
+      </c>
+      <c r="C198" t="n">
         <v>3896</v>
-      </c>
-      <c r="C198" t="n">
-        <v>6332</v>
       </c>
       <c r="D198" t="n">
         <v>4986</v>
       </c>
       <c r="E198" t="n">
-        <v>621</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="199">
@@ -9702,16 +9854,16 @@
         </is>
       </c>
       <c r="B199" t="n">
+        <v>621</v>
+      </c>
+      <c r="C199" t="n">
         <v>3896</v>
-      </c>
-      <c r="C199" t="n">
-        <v>6215</v>
       </c>
       <c r="D199" t="n">
         <v>4986</v>
       </c>
       <c r="E199" t="n">
-        <v>621</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="200">
@@ -9721,16 +9873,16 @@
         </is>
       </c>
       <c r="B200" t="n">
+        <v>621</v>
+      </c>
+      <c r="C200" t="n">
         <v>3896</v>
-      </c>
-      <c r="C200" t="n">
-        <v>6332</v>
       </c>
       <c r="D200" t="n">
         <v>4986</v>
       </c>
       <c r="E200" t="n">
-        <v>621</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="201">
@@ -9740,16 +9892,16 @@
         </is>
       </c>
       <c r="B201" t="n">
+        <v>618</v>
+      </c>
+      <c r="C201" t="n">
         <v>4004</v>
-      </c>
-      <c r="C201" t="n">
-        <v>6282</v>
       </c>
       <c r="D201" t="n">
         <v>4986</v>
       </c>
       <c r="E201" t="n">
-        <v>618</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="202">
@@ -9759,16 +9911,16 @@
         </is>
       </c>
       <c r="B202" t="n">
+        <v>618</v>
+      </c>
+      <c r="C202" t="n">
         <v>4004</v>
-      </c>
-      <c r="C202" t="n">
-        <v>5960</v>
       </c>
       <c r="D202" t="n">
         <v>4986</v>
       </c>
       <c r="E202" t="n">
-        <v>618</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="203">
@@ -9778,16 +9930,16 @@
         </is>
       </c>
       <c r="B203" t="n">
+        <v>618</v>
+      </c>
+      <c r="C203" t="n">
         <v>4004</v>
-      </c>
-      <c r="C203" t="n">
-        <v>6025</v>
       </c>
       <c r="D203" t="n">
         <v>4986</v>
       </c>
       <c r="E203" t="n">
-        <v>618</v>
+        <v>6025</v>
       </c>
     </row>
     <row r="204">
@@ -9797,16 +9949,16 @@
         </is>
       </c>
       <c r="B204" t="n">
+        <v>618</v>
+      </c>
+      <c r="C204" t="n">
         <v>4004</v>
-      </c>
-      <c r="C204" t="n">
-        <v>5981</v>
       </c>
       <c r="D204" t="n">
         <v>5119</v>
       </c>
       <c r="E204" t="n">
-        <v>618</v>
+        <v>5981</v>
       </c>
     </row>
     <row r="205">
@@ -9816,16 +9968,16 @@
         </is>
       </c>
       <c r="B205" t="n">
+        <v>618</v>
+      </c>
+      <c r="C205" t="n">
         <v>4004</v>
-      </c>
-      <c r="C205" t="n">
-        <v>5981</v>
       </c>
       <c r="D205" t="n">
         <v>5119</v>
       </c>
       <c r="E205" t="n">
-        <v>618</v>
+        <v>5981</v>
       </c>
     </row>
     <row r="206">
@@ -9835,16 +9987,16 @@
         </is>
       </c>
       <c r="B206" t="n">
+        <v>620</v>
+      </c>
+      <c r="C206" t="n">
         <v>4004</v>
-      </c>
-      <c r="C206" t="n">
-        <v>6093</v>
       </c>
       <c r="D206" t="n">
         <v>5119</v>
       </c>
       <c r="E206" t="n">
-        <v>620</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="207">
@@ -9854,16 +10006,16 @@
         </is>
       </c>
       <c r="B207" t="n">
+        <v>624</v>
+      </c>
+      <c r="C207" t="n">
         <v>4004</v>
-      </c>
-      <c r="C207" t="n">
-        <v>6093</v>
       </c>
       <c r="D207" t="n">
         <v>5119</v>
       </c>
       <c r="E207" t="n">
-        <v>624</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="208">
@@ -9873,16 +10025,16 @@
         </is>
       </c>
       <c r="B208" t="n">
+        <v>623</v>
+      </c>
+      <c r="C208" t="n">
         <v>4040</v>
-      </c>
-      <c r="C208" t="n">
-        <v>6497</v>
       </c>
       <c r="D208" t="n">
         <v>4986</v>
       </c>
       <c r="E208" t="n">
-        <v>623</v>
+        <v>6497</v>
       </c>
     </row>
     <row r="209">
@@ -9892,16 +10044,16 @@
         </is>
       </c>
       <c r="B209" t="n">
+        <v>622</v>
+      </c>
+      <c r="C209" t="n">
         <v>4040</v>
-      </c>
-      <c r="C209" t="n">
-        <v>6497</v>
       </c>
       <c r="D209" t="n">
         <v>4986</v>
       </c>
       <c r="E209" t="n">
-        <v>622</v>
+        <v>6497</v>
       </c>
     </row>
     <row r="210">
@@ -9911,16 +10063,16 @@
         </is>
       </c>
       <c r="B210" t="n">
+        <v>622</v>
+      </c>
+      <c r="C210" t="n">
         <v>4040</v>
-      </c>
-      <c r="C210" t="n">
-        <v>6497</v>
       </c>
       <c r="D210" t="n">
         <v>4986</v>
       </c>
       <c r="E210" t="n">
-        <v>622</v>
+        <v>6497</v>
       </c>
     </row>
     <row r="211">
@@ -9930,16 +10082,16 @@
         </is>
       </c>
       <c r="B211" t="n">
+        <v>623</v>
+      </c>
+      <c r="C211" t="n">
         <v>4040</v>
-      </c>
-      <c r="C211" t="n">
-        <v>6497</v>
       </c>
       <c r="D211" t="n">
         <v>4986</v>
       </c>
       <c r="E211" t="n">
-        <v>623</v>
+        <v>6497</v>
       </c>
     </row>
     <row r="212">
@@ -9949,16 +10101,16 @@
         </is>
       </c>
       <c r="B212" t="n">
+        <v>623</v>
+      </c>
+      <c r="C212" t="n">
         <v>4040</v>
-      </c>
-      <c r="C212" t="n">
-        <v>6497</v>
       </c>
       <c r="D212" t="n">
         <v>4986</v>
       </c>
       <c r="E212" t="n">
-        <v>623</v>
+        <v>6497</v>
       </c>
     </row>
     <row r="213">
@@ -9968,16 +10120,16 @@
         </is>
       </c>
       <c r="B213" t="n">
+        <v>623</v>
+      </c>
+      <c r="C213" t="n">
         <v>4040</v>
-      </c>
-      <c r="C213" t="n">
-        <v>6544</v>
       </c>
       <c r="D213" t="n">
         <v>4986</v>
       </c>
       <c r="E213" t="n">
-        <v>623</v>
+        <v>6544</v>
       </c>
     </row>
     <row r="214">
@@ -9987,16 +10139,16 @@
         </is>
       </c>
       <c r="B214" t="n">
+        <v>623</v>
+      </c>
+      <c r="C214" t="n">
         <v>4040</v>
-      </c>
-      <c r="C214" t="n">
-        <v>6592</v>
       </c>
       <c r="D214" t="n">
         <v>4986</v>
       </c>
       <c r="E214" t="n">
-        <v>623</v>
+        <v>6592</v>
       </c>
     </row>
     <row r="215">
@@ -10006,16 +10158,16 @@
         </is>
       </c>
       <c r="B215" t="n">
+        <v>623</v>
+      </c>
+      <c r="C215" t="n">
         <v>4040</v>
-      </c>
-      <c r="C215" t="n">
-        <v>6640</v>
       </c>
       <c r="D215" t="n">
         <v>4986</v>
       </c>
       <c r="E215" t="n">
-        <v>623</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="216">
@@ -10025,16 +10177,16 @@
         </is>
       </c>
       <c r="B216" t="n">
+        <v>623</v>
+      </c>
+      <c r="C216" t="n">
         <v>4040</v>
-      </c>
-      <c r="C216" t="n">
-        <v>6640</v>
       </c>
       <c r="D216" t="n">
         <v>4986</v>
       </c>
       <c r="E216" t="n">
-        <v>623</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="217">
@@ -10044,16 +10196,16 @@
         </is>
       </c>
       <c r="B217" t="n">
+        <v>620</v>
+      </c>
+      <c r="C217" t="n">
         <v>4040</v>
-      </c>
-      <c r="C217" t="n">
-        <v>6640</v>
       </c>
       <c r="D217" t="n">
         <v>4986</v>
       </c>
       <c r="E217" t="n">
-        <v>620</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="218">
@@ -10063,16 +10215,16 @@
         </is>
       </c>
       <c r="B218" t="n">
+        <v>616</v>
+      </c>
+      <c r="C218" t="n">
         <v>4040</v>
-      </c>
-      <c r="C218" t="n">
-        <v>6640</v>
       </c>
       <c r="D218" t="n">
         <v>4986</v>
       </c>
       <c r="E218" t="n">
-        <v>616</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="219">
@@ -10082,16 +10234,16 @@
         </is>
       </c>
       <c r="B219" t="n">
+        <v>611</v>
+      </c>
+      <c r="C219" t="n">
         <v>4040</v>
-      </c>
-      <c r="C219" t="n">
-        <v>6640</v>
       </c>
       <c r="D219" t="n">
         <v>4986</v>
       </c>
       <c r="E219" t="n">
-        <v>611</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="220">
@@ -10101,16 +10253,16 @@
         </is>
       </c>
       <c r="B220" t="n">
+        <v>606</v>
+      </c>
+      <c r="C220" t="n">
         <v>4040</v>
-      </c>
-      <c r="C220" t="n">
-        <v>6684</v>
       </c>
       <c r="D220" t="n">
         <v>4986</v>
       </c>
       <c r="E220" t="n">
-        <v>606</v>
+        <v>6684</v>
       </c>
     </row>
     <row r="221">
@@ -10120,16 +10272,16 @@
         </is>
       </c>
       <c r="B221" t="n">
+        <v>606</v>
+      </c>
+      <c r="C221" t="n">
         <v>4040</v>
-      </c>
-      <c r="C221" t="n">
-        <v>6684</v>
       </c>
       <c r="D221" t="n">
         <v>4986</v>
       </c>
       <c r="E221" t="n">
-        <v>606</v>
+        <v>6684</v>
       </c>
     </row>
     <row r="222">
@@ -10139,16 +10291,16 @@
         </is>
       </c>
       <c r="B222" t="n">
+        <v>606</v>
+      </c>
+      <c r="C222" t="n">
         <v>4040</v>
-      </c>
-      <c r="C222" t="n">
-        <v>6905</v>
       </c>
       <c r="D222" t="n">
         <v>4986</v>
       </c>
       <c r="E222" t="n">
-        <v>606</v>
+        <v>6905</v>
       </c>
     </row>
     <row r="223">
@@ -10158,16 +10310,16 @@
         </is>
       </c>
       <c r="B223" t="n">
+        <v>606</v>
+      </c>
+      <c r="C223" t="n">
         <v>4040</v>
-      </c>
-      <c r="C223" t="n">
-        <v>6951</v>
       </c>
       <c r="D223" t="n">
         <v>4986</v>
       </c>
       <c r="E223" t="n">
-        <v>606</v>
+        <v>6951</v>
       </c>
     </row>
     <row r="224">
@@ -10177,16 +10329,16 @@
         </is>
       </c>
       <c r="B224" t="n">
+        <v>606</v>
+      </c>
+      <c r="C224" t="n">
         <v>4040</v>
-      </c>
-      <c r="C224" t="n">
-        <v>6951</v>
       </c>
       <c r="D224" t="n">
         <v>4986</v>
       </c>
       <c r="E224" t="n">
-        <v>606</v>
+        <v>6951</v>
       </c>
     </row>
     <row r="225">
@@ -10196,16 +10348,16 @@
         </is>
       </c>
       <c r="B225" t="n">
+        <v>609</v>
+      </c>
+      <c r="C225" t="n">
         <v>4040</v>
-      </c>
-      <c r="C225" t="n">
-        <v>6998</v>
       </c>
       <c r="D225" t="n">
         <v>4952</v>
       </c>
       <c r="E225" t="n">
-        <v>609</v>
+        <v>6998</v>
       </c>
     </row>
     <row r="226">
@@ -10215,16 +10367,16 @@
         </is>
       </c>
       <c r="B226" t="n">
+        <v>609</v>
+      </c>
+      <c r="C226" t="n">
         <v>4040</v>
-      </c>
-      <c r="C226" t="n">
-        <v>7198</v>
       </c>
       <c r="D226" t="n">
         <v>4952</v>
       </c>
       <c r="E226" t="n">
-        <v>609</v>
+        <v>7198</v>
       </c>
     </row>
     <row r="227">
@@ -10234,16 +10386,16 @@
         </is>
       </c>
       <c r="B227" t="n">
+        <v>609</v>
+      </c>
+      <c r="C227" t="n">
         <v>4040</v>
-      </c>
-      <c r="C227" t="n">
-        <v>7501</v>
       </c>
       <c r="D227" t="n">
         <v>4952</v>
       </c>
       <c r="E227" t="n">
-        <v>609</v>
+        <v>7501</v>
       </c>
     </row>
     <row r="228">
@@ -10253,16 +10405,16 @@
         </is>
       </c>
       <c r="B228" t="n">
+        <v>609</v>
+      </c>
+      <c r="C228" t="n">
         <v>4040</v>
-      </c>
-      <c r="C228" t="n">
-        <v>7501</v>
       </c>
       <c r="D228" t="n">
         <v>4952</v>
       </c>
       <c r="E228" t="n">
-        <v>609</v>
+        <v>7501</v>
       </c>
     </row>
     <row r="229">
@@ -10272,16 +10424,16 @@
         </is>
       </c>
       <c r="B229" t="n">
+        <v>609</v>
+      </c>
+      <c r="C229" t="n">
         <v>4040</v>
-      </c>
-      <c r="C229" t="n">
-        <v>7501</v>
       </c>
       <c r="D229" t="n">
         <v>4952</v>
       </c>
       <c r="E229" t="n">
-        <v>609</v>
+        <v>7501</v>
       </c>
     </row>
     <row r="230">
@@ -10291,16 +10443,16 @@
         </is>
       </c>
       <c r="B230" t="n">
+        <v>609</v>
+      </c>
+      <c r="C230" t="n">
         <v>4040</v>
-      </c>
-      <c r="C230" t="n">
-        <v>7548</v>
       </c>
       <c r="D230" t="n">
         <v>4952</v>
       </c>
       <c r="E230" t="n">
-        <v>609</v>
+        <v>7548</v>
       </c>
     </row>
     <row r="231">
@@ -10310,16 +10462,16 @@
         </is>
       </c>
       <c r="B231" t="n">
+        <v>609</v>
+      </c>
+      <c r="C231" t="n">
         <v>4040</v>
-      </c>
-      <c r="C231" t="n">
-        <v>7548</v>
       </c>
       <c r="D231" t="n">
         <v>4952</v>
       </c>
       <c r="E231" t="n">
-        <v>609</v>
+        <v>7548</v>
       </c>
     </row>
     <row r="232">
@@ -10329,16 +10481,16 @@
         </is>
       </c>
       <c r="B232" t="n">
+        <v>609</v>
+      </c>
+      <c r="C232" t="n">
         <v>4040</v>
-      </c>
-      <c r="C232" t="n">
-        <v>7548</v>
       </c>
       <c r="D232" t="n">
         <v>4952</v>
       </c>
       <c r="E232" t="n">
-        <v>609</v>
+        <v>7548</v>
       </c>
     </row>
     <row r="233">
@@ -10348,16 +10500,16 @@
         </is>
       </c>
       <c r="B233" t="n">
+        <v>609</v>
+      </c>
+      <c r="C233" t="n">
         <v>4040</v>
-      </c>
-      <c r="C233" t="n">
-        <v>7548</v>
       </c>
       <c r="D233" t="n">
         <v>4952</v>
       </c>
       <c r="E233" t="n">
-        <v>609</v>
+        <v>7548</v>
       </c>
     </row>
     <row r="234">
@@ -10367,16 +10519,16 @@
         </is>
       </c>
       <c r="B234" t="n">
+        <v>609</v>
+      </c>
+      <c r="C234" t="n">
         <v>4040</v>
-      </c>
-      <c r="C234" t="n">
-        <v>7548</v>
       </c>
       <c r="D234" t="n">
         <v>4952</v>
       </c>
       <c r="E234" t="n">
-        <v>609</v>
+        <v>7548</v>
       </c>
     </row>
     <row r="235">
@@ -10386,16 +10538,16 @@
         </is>
       </c>
       <c r="B235" t="n">
+        <v>609</v>
+      </c>
+      <c r="C235" t="n">
         <v>4040</v>
-      </c>
-      <c r="C235" t="n">
-        <v>7548</v>
       </c>
       <c r="D235" t="n">
         <v>4952</v>
       </c>
       <c r="E235" t="n">
-        <v>609</v>
+        <v>7548</v>
       </c>
     </row>
     <row r="236">
@@ -10405,16 +10557,16 @@
         </is>
       </c>
       <c r="B236" t="n">
+        <v>603</v>
+      </c>
+      <c r="C236" t="n">
         <v>4040</v>
-      </c>
-      <c r="C236" t="n">
-        <v>7731</v>
       </c>
       <c r="D236" t="n">
         <v>4952</v>
       </c>
       <c r="E236" t="n">
-        <v>603</v>
+        <v>7731</v>
       </c>
     </row>
     <row r="237">
@@ -10424,16 +10576,16 @@
         </is>
       </c>
       <c r="B237" t="n">
+        <v>603</v>
+      </c>
+      <c r="C237" t="n">
         <v>4040</v>
-      </c>
-      <c r="C237" t="n">
-        <v>10031</v>
       </c>
       <c r="D237" t="n">
         <v>4952</v>
       </c>
       <c r="E237" t="n">
-        <v>603</v>
+        <v>10031</v>
       </c>
     </row>
     <row r="238">
@@ -10443,16 +10595,16 @@
         </is>
       </c>
       <c r="B238" t="n">
+        <v>603</v>
+      </c>
+      <c r="C238" t="n">
         <v>4069</v>
-      </c>
-      <c r="C238" t="n">
-        <v>10031</v>
       </c>
       <c r="D238" t="n">
         <v>4952</v>
       </c>
       <c r="E238" t="n">
-        <v>603</v>
+        <v>10031</v>
       </c>
     </row>
     <row r="239">
@@ -10462,16 +10614,16 @@
         </is>
       </c>
       <c r="B239" t="n">
+        <v>603</v>
+      </c>
+      <c r="C239" t="n">
         <v>4069</v>
-      </c>
-      <c r="C239" t="n">
-        <v>10583</v>
       </c>
       <c r="D239" t="n">
         <v>4952</v>
       </c>
       <c r="E239" t="n">
-        <v>603</v>
+        <v>10583</v>
       </c>
     </row>
     <row r="240">
@@ -10481,16 +10633,16 @@
         </is>
       </c>
       <c r="B240" t="n">
+        <v>603</v>
+      </c>
+      <c r="C240" t="n">
         <v>4069</v>
-      </c>
-      <c r="C240" t="n">
-        <v>10753</v>
       </c>
       <c r="D240" t="n">
         <v>4952</v>
       </c>
       <c r="E240" t="n">
-        <v>603</v>
+        <v>10753</v>
       </c>
     </row>
     <row r="241">
@@ -10500,16 +10652,16 @@
         </is>
       </c>
       <c r="B241" t="n">
+        <v>607</v>
+      </c>
+      <c r="C241" t="n">
         <v>4110</v>
-      </c>
-      <c r="C241" t="n">
-        <v>10728</v>
       </c>
       <c r="D241" t="n">
         <v>4952</v>
       </c>
       <c r="E241" t="n">
-        <v>607</v>
+        <v>10728</v>
       </c>
     </row>
     <row r="242">
@@ -10519,16 +10671,16 @@
         </is>
       </c>
       <c r="B242" t="n">
+        <v>615</v>
+      </c>
+      <c r="C242" t="n">
         <v>4110</v>
-      </c>
-      <c r="C242" t="n">
-        <v>10671</v>
       </c>
       <c r="D242" t="n">
         <v>4952</v>
       </c>
       <c r="E242" t="n">
-        <v>615</v>
+        <v>10671</v>
       </c>
     </row>
     <row r="243">
@@ -10538,16 +10690,16 @@
         </is>
       </c>
       <c r="B243" t="n">
+        <v>615</v>
+      </c>
+      <c r="C243" t="n">
         <v>4038</v>
-      </c>
-      <c r="C243" t="n">
-        <v>10850</v>
       </c>
       <c r="D243" t="n">
         <v>4952</v>
       </c>
       <c r="E243" t="n">
-        <v>615</v>
+        <v>10850</v>
       </c>
     </row>
     <row r="244">
@@ -10557,16 +10709,16 @@
         </is>
       </c>
       <c r="B244" t="n">
+        <v>619</v>
+      </c>
+      <c r="C244" t="n">
         <v>4038</v>
-      </c>
-      <c r="C244" t="n">
-        <v>10850</v>
       </c>
       <c r="D244" t="n">
         <v>4952</v>
       </c>
       <c r="E244" t="n">
-        <v>619</v>
+        <v>10850</v>
       </c>
     </row>
     <row r="245">
@@ -10576,16 +10728,16 @@
         </is>
       </c>
       <c r="B245" t="n">
+        <v>615</v>
+      </c>
+      <c r="C245" t="n">
         <v>4038</v>
-      </c>
-      <c r="C245" t="n">
-        <v>10850</v>
       </c>
       <c r="D245" t="n">
         <v>4951</v>
       </c>
       <c r="E245" t="n">
-        <v>615</v>
+        <v>10850</v>
       </c>
     </row>
     <row r="246">
@@ -10595,16 +10747,16 @@
         </is>
       </c>
       <c r="B246" t="n">
+        <v>615</v>
+      </c>
+      <c r="C246" t="n">
         <v>4038</v>
-      </c>
-      <c r="C246" t="n">
-        <v>10850</v>
       </c>
       <c r="D246" t="n">
         <v>4951</v>
       </c>
       <c r="E246" t="n">
-        <v>615</v>
+        <v>10850</v>
       </c>
     </row>
     <row r="247">
@@ -10614,16 +10766,16 @@
         </is>
       </c>
       <c r="B247" t="n">
+        <v>619</v>
+      </c>
+      <c r="C247" t="n">
         <v>4038</v>
-      </c>
-      <c r="C247" t="n">
-        <v>10850</v>
       </c>
       <c r="D247" t="n">
         <v>4951</v>
       </c>
       <c r="E247" t="n">
-        <v>619</v>
+        <v>10850</v>
       </c>
     </row>
     <row r="248">
@@ -10633,16 +10785,16 @@
         </is>
       </c>
       <c r="B248" t="n">
+        <v>623</v>
+      </c>
+      <c r="C248" t="n">
         <v>4038</v>
-      </c>
-      <c r="C248" t="n">
-        <v>11181</v>
       </c>
       <c r="D248" t="n">
         <v>4951</v>
       </c>
       <c r="E248" t="n">
-        <v>623</v>
+        <v>11181</v>
       </c>
     </row>
     <row r="249">
@@ -10652,16 +10804,16 @@
         </is>
       </c>
       <c r="B249" t="n">
+        <v>614</v>
+      </c>
+      <c r="C249" t="n">
         <v>4038</v>
-      </c>
-      <c r="C249" t="n">
-        <v>11242</v>
       </c>
       <c r="D249" t="n">
         <v>4951</v>
       </c>
       <c r="E249" t="n">
-        <v>614</v>
+        <v>11242</v>
       </c>
     </row>
     <row r="250">
@@ -10671,16 +10823,16 @@
         </is>
       </c>
       <c r="B250" t="n">
+        <v>614</v>
+      </c>
+      <c r="C250" t="n">
         <v>4038</v>
-      </c>
-      <c r="C250" t="n">
-        <v>11242</v>
       </c>
       <c r="D250" t="n">
         <v>4951</v>
       </c>
       <c r="E250" t="n">
-        <v>614</v>
+        <v>11242</v>
       </c>
     </row>
     <row r="251">
@@ -10690,16 +10842,16 @@
         </is>
       </c>
       <c r="B251" t="n">
+        <v>622</v>
+      </c>
+      <c r="C251" t="n">
         <v>4038</v>
-      </c>
-      <c r="C251" t="n">
-        <v>11242</v>
       </c>
       <c r="D251" t="n">
         <v>4951</v>
       </c>
       <c r="E251" t="n">
-        <v>622</v>
+        <v>11242</v>
       </c>
     </row>
     <row r="252">
@@ -10709,16 +10861,16 @@
         </is>
       </c>
       <c r="B252" t="n">
+        <v>613</v>
+      </c>
+      <c r="C252" t="n">
         <v>4038</v>
-      </c>
-      <c r="C252" t="n">
-        <v>11080</v>
       </c>
       <c r="D252" t="n">
         <v>4951</v>
       </c>
       <c r="E252" t="n">
-        <v>613</v>
+        <v>11080</v>
       </c>
     </row>
     <row r="253">
@@ -10728,16 +10880,16 @@
         </is>
       </c>
       <c r="B253" t="n">
+        <v>615</v>
+      </c>
+      <c r="C253" t="n">
         <v>4038</v>
-      </c>
-      <c r="C253" t="n">
-        <v>10910</v>
       </c>
       <c r="D253" t="n">
         <v>4951</v>
       </c>
       <c r="E253" t="n">
-        <v>615</v>
+        <v>10910</v>
       </c>
     </row>
     <row r="254">
@@ -10747,16 +10899,16 @@
         </is>
       </c>
       <c r="B254" t="n">
+        <v>615</v>
+      </c>
+      <c r="C254" t="n">
         <v>4038</v>
-      </c>
-      <c r="C254" t="n">
-        <v>10910</v>
       </c>
       <c r="D254" t="n">
         <v>4951</v>
       </c>
       <c r="E254" t="n">
-        <v>615</v>
+        <v>10910</v>
       </c>
     </row>
     <row r="255">
@@ -10766,16 +10918,16 @@
         </is>
       </c>
       <c r="B255" t="n">
+        <v>615</v>
+      </c>
+      <c r="C255" t="n">
         <v>4038</v>
-      </c>
-      <c r="C255" t="n">
-        <v>10625</v>
       </c>
       <c r="D255" t="n">
         <v>4951</v>
       </c>
       <c r="E255" t="n">
-        <v>615</v>
+        <v>10625</v>
       </c>
     </row>
     <row r="256">
@@ -10785,16 +10937,16 @@
         </is>
       </c>
       <c r="B256" t="n">
+        <v>614</v>
+      </c>
+      <c r="C256" t="n">
         <v>4038</v>
-      </c>
-      <c r="C256" t="n">
-        <v>10625</v>
       </c>
       <c r="D256" t="n">
         <v>4951</v>
       </c>
       <c r="E256" t="n">
-        <v>614</v>
+        <v>10625</v>
       </c>
     </row>
     <row r="257">
@@ -10804,16 +10956,16 @@
         </is>
       </c>
       <c r="B257" t="n">
+        <v>616</v>
+      </c>
+      <c r="C257" t="n">
         <v>4038</v>
-      </c>
-      <c r="C257" t="n">
-        <v>10669</v>
       </c>
       <c r="D257" t="n">
         <v>4951</v>
       </c>
       <c r="E257" t="n">
-        <v>616</v>
+        <v>10669</v>
       </c>
     </row>
     <row r="258">
@@ -10823,16 +10975,16 @@
         </is>
       </c>
       <c r="B258" t="n">
+        <v>612</v>
+      </c>
+      <c r="C258" t="n">
         <v>4038</v>
-      </c>
-      <c r="C258" t="n">
-        <v>10669</v>
       </c>
       <c r="D258" t="n">
         <v>4951</v>
       </c>
       <c r="E258" t="n">
-        <v>612</v>
+        <v>10669</v>
       </c>
     </row>
     <row r="259">
@@ -10842,16 +10994,16 @@
         </is>
       </c>
       <c r="B259" t="n">
+        <v>612</v>
+      </c>
+      <c r="C259" t="n">
         <v>4038</v>
-      </c>
-      <c r="C259" t="n">
-        <v>10669</v>
       </c>
       <c r="D259" t="n">
         <v>4951</v>
       </c>
       <c r="E259" t="n">
-        <v>612</v>
+        <v>10669</v>
       </c>
     </row>
     <row r="260">
@@ -10861,16 +11013,16 @@
         </is>
       </c>
       <c r="B260" t="n">
+        <v>612</v>
+      </c>
+      <c r="C260" t="n">
         <v>4038</v>
-      </c>
-      <c r="C260" t="n">
-        <v>10844</v>
       </c>
       <c r="D260" t="n">
         <v>4951</v>
       </c>
       <c r="E260" t="n">
-        <v>612</v>
+        <v>10844</v>
       </c>
     </row>
     <row r="261">
@@ -10880,16 +11032,16 @@
         </is>
       </c>
       <c r="B261" t="n">
+        <v>612</v>
+      </c>
+      <c r="C261" t="n">
         <v>4038</v>
-      </c>
-      <c r="C261" t="n">
-        <v>10844</v>
       </c>
       <c r="D261" t="n">
         <v>4951</v>
       </c>
       <c r="E261" t="n">
-        <v>612</v>
+        <v>10844</v>
       </c>
     </row>
     <row r="262">
@@ -10899,16 +11051,16 @@
         </is>
       </c>
       <c r="B262" t="n">
+        <v>612</v>
+      </c>
+      <c r="C262" t="n">
         <v>4038</v>
-      </c>
-      <c r="C262" t="n">
-        <v>10844</v>
       </c>
       <c r="D262" t="n">
         <v>4951</v>
       </c>
       <c r="E262" t="n">
-        <v>612</v>
+        <v>10844</v>
       </c>
     </row>
     <row r="263">
@@ -10918,16 +11070,16 @@
         </is>
       </c>
       <c r="B263" t="n">
+        <v>612</v>
+      </c>
+      <c r="C263" t="n">
         <v>4038</v>
-      </c>
-      <c r="C263" t="n">
-        <v>10844</v>
       </c>
       <c r="D263" t="n">
         <v>4951</v>
       </c>
       <c r="E263" t="n">
-        <v>612</v>
+        <v>10844</v>
       </c>
     </row>
     <row r="264">
@@ -10937,16 +11089,16 @@
         </is>
       </c>
       <c r="B264" t="n">
+        <v>612</v>
+      </c>
+      <c r="C264" t="n">
         <v>4038</v>
-      </c>
-      <c r="C264" t="n">
-        <v>10844</v>
       </c>
       <c r="D264" t="n">
         <v>4951</v>
       </c>
       <c r="E264" t="n">
-        <v>612</v>
+        <v>10844</v>
       </c>
     </row>
     <row r="265">
@@ -10956,16 +11108,16 @@
         </is>
       </c>
       <c r="B265" t="n">
+        <v>612</v>
+      </c>
+      <c r="C265" t="n">
         <v>4038</v>
-      </c>
-      <c r="C265" t="n">
-        <v>10844</v>
       </c>
       <c r="D265" t="n">
         <v>4951</v>
       </c>
       <c r="E265" t="n">
-        <v>612</v>
+        <v>10844</v>
       </c>
     </row>
     <row r="266">
@@ -10975,16 +11127,16 @@
         </is>
       </c>
       <c r="B266" t="n">
+        <v>612</v>
+      </c>
+      <c r="C266" t="n">
         <v>4038</v>
-      </c>
-      <c r="C266" t="n">
-        <v>10844</v>
       </c>
       <c r="D266" t="n">
         <v>4951</v>
       </c>
       <c r="E266" t="n">
-        <v>612</v>
+        <v>10844</v>
       </c>
     </row>
     <row r="267">
@@ -10994,16 +11146,16 @@
         </is>
       </c>
       <c r="B267" t="n">
+        <v>612</v>
+      </c>
+      <c r="C267" t="n">
         <v>4038</v>
-      </c>
-      <c r="C267" t="n">
-        <v>10844</v>
       </c>
       <c r="D267" t="n">
         <v>4951</v>
       </c>
       <c r="E267" t="n">
-        <v>612</v>
+        <v>10844</v>
       </c>
     </row>
     <row r="268">
@@ -11013,16 +11165,16 @@
         </is>
       </c>
       <c r="B268" t="n">
+        <v>612</v>
+      </c>
+      <c r="C268" t="n">
         <v>4038</v>
-      </c>
-      <c r="C268" t="n">
-        <v>11716</v>
       </c>
       <c r="D268" t="n">
         <v>4951</v>
       </c>
       <c r="E268" t="n">
-        <v>612</v>
+        <v>11716</v>
       </c>
     </row>
     <row r="269">
@@ -11032,16 +11184,16 @@
         </is>
       </c>
       <c r="B269" t="n">
+        <v>608</v>
+      </c>
+      <c r="C269" t="n">
         <v>4038</v>
-      </c>
-      <c r="C269" t="n">
-        <v>11921</v>
       </c>
       <c r="D269" t="n">
         <v>4951</v>
       </c>
       <c r="E269" t="n">
-        <v>608</v>
+        <v>11921</v>
       </c>
     </row>
     <row r="270">
@@ -11051,16 +11203,16 @@
         </is>
       </c>
       <c r="B270" t="n">
+        <v>608</v>
+      </c>
+      <c r="C270" t="n">
         <v>4038</v>
-      </c>
-      <c r="C270" t="n">
-        <v>11921</v>
       </c>
       <c r="D270" t="n">
         <v>4951</v>
       </c>
       <c r="E270" t="n">
-        <v>608</v>
+        <v>11921</v>
       </c>
     </row>
     <row r="271">
@@ -11070,16 +11222,16 @@
         </is>
       </c>
       <c r="B271" t="n">
+        <v>608</v>
+      </c>
+      <c r="C271" t="n">
         <v>4046</v>
-      </c>
-      <c r="C271" t="n">
-        <v>12090</v>
       </c>
       <c r="D271" t="n">
         <v>4951</v>
       </c>
       <c r="E271" t="n">
-        <v>608</v>
+        <v>12090</v>
       </c>
     </row>
     <row r="272">
@@ -11089,16 +11241,16 @@
         </is>
       </c>
       <c r="B272" t="n">
+        <v>610</v>
+      </c>
+      <c r="C272" t="n">
         <v>4046</v>
-      </c>
-      <c r="C272" t="n">
-        <v>12137</v>
       </c>
       <c r="D272" t="n">
         <v>4951</v>
       </c>
       <c r="E272" t="n">
-        <v>610</v>
+        <v>12137</v>
       </c>
     </row>
     <row r="273">
@@ -11108,16 +11260,16 @@
         </is>
       </c>
       <c r="B273" t="n">
+        <v>610</v>
+      </c>
+      <c r="C273" t="n">
         <v>4046</v>
-      </c>
-      <c r="C273" t="n">
-        <v>12137</v>
       </c>
       <c r="D273" t="n">
         <v>4951</v>
       </c>
       <c r="E273" t="n">
-        <v>610</v>
+        <v>12137</v>
       </c>
     </row>
     <row r="274">
@@ -11127,16 +11279,16 @@
         </is>
       </c>
       <c r="B274" t="n">
+        <v>610</v>
+      </c>
+      <c r="C274" t="n">
         <v>4046</v>
-      </c>
-      <c r="C274" t="n">
-        <v>12168</v>
       </c>
       <c r="D274" t="n">
         <v>5065</v>
       </c>
       <c r="E274" t="n">
-        <v>610</v>
+        <v>12168</v>
       </c>
     </row>
     <row r="275">
@@ -11146,16 +11298,16 @@
         </is>
       </c>
       <c r="B275" t="n">
+        <v>610</v>
+      </c>
+      <c r="C275" t="n">
         <v>4046</v>
-      </c>
-      <c r="C275" t="n">
-        <v>12168</v>
       </c>
       <c r="D275" t="n">
         <v>5065</v>
       </c>
       <c r="E275" t="n">
-        <v>610</v>
+        <v>12168</v>
       </c>
     </row>
     <row r="276">
@@ -11165,16 +11317,16 @@
         </is>
       </c>
       <c r="B276" t="n">
+        <v>615</v>
+      </c>
+      <c r="C276" t="n">
         <v>3982</v>
-      </c>
-      <c r="C276" t="n">
-        <v>12270</v>
       </c>
       <c r="D276" t="n">
         <v>5125</v>
       </c>
       <c r="E276" t="n">
-        <v>615</v>
+        <v>12270</v>
       </c>
     </row>
     <row r="277">
@@ -11184,16 +11336,16 @@
         </is>
       </c>
       <c r="B277" t="n">
+        <v>616</v>
+      </c>
+      <c r="C277" t="n">
         <v>3989</v>
-      </c>
-      <c r="C277" t="n">
-        <v>12174</v>
       </c>
       <c r="D277" t="n">
         <v>5125</v>
       </c>
       <c r="E277" t="n">
-        <v>616</v>
+        <v>12174</v>
       </c>
     </row>
     <row r="278">
@@ -11203,16 +11355,16 @@
         </is>
       </c>
       <c r="B278" t="n">
+        <v>616</v>
+      </c>
+      <c r="C278" t="n">
         <v>3989</v>
-      </c>
-      <c r="C278" t="n">
-        <v>12174</v>
       </c>
       <c r="D278" t="n">
         <v>5125</v>
       </c>
       <c r="E278" t="n">
-        <v>616</v>
+        <v>12174</v>
       </c>
     </row>
     <row r="279">
@@ -11222,16 +11374,16 @@
         </is>
       </c>
       <c r="B279" t="n">
+        <v>616</v>
+      </c>
+      <c r="C279" t="n">
         <v>3989</v>
-      </c>
-      <c r="C279" t="n">
-        <v>12174</v>
       </c>
       <c r="D279" t="n">
         <v>5125</v>
       </c>
       <c r="E279" t="n">
-        <v>616</v>
+        <v>12174</v>
       </c>
     </row>
     <row r="280">
@@ -11241,16 +11393,16 @@
         </is>
       </c>
       <c r="B280" t="n">
+        <v>616</v>
+      </c>
+      <c r="C280" t="n">
         <v>3989</v>
-      </c>
-      <c r="C280" t="n">
-        <v>12174</v>
       </c>
       <c r="D280" t="n">
         <v>5125</v>
       </c>
       <c r="E280" t="n">
-        <v>616</v>
+        <v>12174</v>
       </c>
     </row>
     <row r="281">
@@ -11260,16 +11412,16 @@
         </is>
       </c>
       <c r="B281" t="n">
+        <v>616</v>
+      </c>
+      <c r="C281" t="n">
         <v>3989</v>
-      </c>
-      <c r="C281" t="n">
-        <v>12188</v>
       </c>
       <c r="D281" t="n">
         <v>5125</v>
       </c>
       <c r="E281" t="n">
-        <v>616</v>
+        <v>12188</v>
       </c>
     </row>
     <row r="282">
@@ -11279,16 +11431,16 @@
         </is>
       </c>
       <c r="B282" t="n">
+        <v>616</v>
+      </c>
+      <c r="C282" t="n">
         <v>3989</v>
-      </c>
-      <c r="C282" t="n">
-        <v>12188</v>
       </c>
       <c r="D282" t="n">
         <v>5125</v>
       </c>
       <c r="E282" t="n">
-        <v>616</v>
+        <v>12188</v>
       </c>
     </row>
     <row r="283">
@@ -11298,16 +11450,16 @@
         </is>
       </c>
       <c r="B283" t="n">
+        <v>616</v>
+      </c>
+      <c r="C283" t="n">
         <v>3989</v>
-      </c>
-      <c r="C283" t="n">
-        <v>12188</v>
       </c>
       <c r="D283" t="n">
         <v>5125</v>
       </c>
       <c r="E283" t="n">
-        <v>616</v>
+        <v>12188</v>
       </c>
     </row>
     <row r="284">
@@ -11317,16 +11469,16 @@
         </is>
       </c>
       <c r="B284" t="n">
+        <v>616</v>
+      </c>
+      <c r="C284" t="n">
         <v>3989</v>
-      </c>
-      <c r="C284" t="n">
-        <v>12191</v>
       </c>
       <c r="D284" t="n">
         <v>5125</v>
       </c>
       <c r="E284" t="n">
-        <v>616</v>
+        <v>12191</v>
       </c>
     </row>
     <row r="285">
@@ -11336,16 +11488,16 @@
         </is>
       </c>
       <c r="B285" t="n">
+        <v>616</v>
+      </c>
+      <c r="C285" t="n">
         <v>3989</v>
-      </c>
-      <c r="C285" t="n">
-        <v>12191</v>
       </c>
       <c r="D285" t="n">
         <v>5125</v>
       </c>
       <c r="E285" t="n">
-        <v>616</v>
+        <v>12191</v>
       </c>
     </row>
     <row r="286">
@@ -11355,16 +11507,16 @@
         </is>
       </c>
       <c r="B286" t="n">
+        <v>618</v>
+      </c>
+      <c r="C286" t="n">
         <v>3989</v>
-      </c>
-      <c r="C286" t="n">
-        <v>12270</v>
       </c>
       <c r="D286" t="n">
         <v>5125</v>
       </c>
       <c r="E286" t="n">
-        <v>618</v>
+        <v>12270</v>
       </c>
     </row>
     <row r="287">
@@ -11374,16 +11526,16 @@
         </is>
       </c>
       <c r="B287" t="n">
+        <v>618</v>
+      </c>
+      <c r="C287" t="n">
         <v>3989</v>
-      </c>
-      <c r="C287" t="n">
-        <v>12285</v>
       </c>
       <c r="D287" t="n">
         <v>5125</v>
       </c>
       <c r="E287" t="n">
-        <v>618</v>
+        <v>12285</v>
       </c>
     </row>
     <row r="288">
@@ -11393,16 +11545,168 @@
         </is>
       </c>
       <c r="B288" t="n">
+        <v>618</v>
+      </c>
+      <c r="C288" t="n">
         <v>3989</v>
-      </c>
-      <c r="C288" t="n">
-        <v>12285</v>
       </c>
       <c r="D288" t="n">
         <v>5125</v>
       </c>
       <c r="E288" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
         <v>618</v>
+      </c>
+      <c r="C289" t="n">
+        <v>3989</v>
+      </c>
+      <c r="D289" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E289" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>618</v>
+      </c>
+      <c r="C290" t="n">
+        <v>3989</v>
+      </c>
+      <c r="D290" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E290" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>618</v>
+      </c>
+      <c r="C291" t="n">
+        <v>3989</v>
+      </c>
+      <c r="D291" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E291" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>618</v>
+      </c>
+      <c r="C292" t="n">
+        <v>3989</v>
+      </c>
+      <c r="D292" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E292" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>620</v>
+      </c>
+      <c r="C293" t="n">
+        <v>4026</v>
+      </c>
+      <c r="D293" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E293" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>621</v>
+      </c>
+      <c r="C294" t="n">
+        <v>4026</v>
+      </c>
+      <c r="D294" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E294" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>621</v>
+      </c>
+      <c r="C295" t="n">
+        <v>4026</v>
+      </c>
+      <c r="D295" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E295" t="n">
+        <v>12285</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>621</v>
+      </c>
+      <c r="C296" t="n">
+        <v>4026</v>
+      </c>
+      <c r="D296" t="n">
+        <v>5125</v>
+      </c>
+      <c r="E296" t="n">
+        <v>12285</v>
       </c>
     </row>
   </sheetData>
